--- a/files/NRL_try_channel_matchups.xlsx
+++ b/files/NRL_try_channel_matchups.xlsx
@@ -2509,7 +2509,7 @@
         <v>28</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>3.8587</v>
+        <v>3.8628</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>6</v>
@@ -2542,7 +2542,7 @@
         <v>1.0067</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.6276</v>
+        <v>0.6283</v>
       </c>
       <c r="T2" s="3" t="s">
         <v>89</v>
@@ -2577,7 +2577,7 @@
         <v>28</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>3.8587</v>
+        <v>3.8628</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
@@ -2610,7 +2610,7 @@
         <v>0.5569</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.1865</v>
+        <v>0.1867</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>92</v>
@@ -2645,7 +2645,7 @@
         <v>28</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>3.8587</v>
+        <v>3.8628</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>12</v>
@@ -2678,7 +2678,7 @@
         <v>1.344</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.5363</v>
+        <v>0.5369</v>
       </c>
       <c r="T4" s="3" t="s">
         <v>95</v>
@@ -2713,7 +2713,7 @@
         <v>28</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3.8587</v>
+        <v>3.8628</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
@@ -2746,7 +2746,7 @@
         <v>0.9067</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.3287</v>
+        <v>0.3291</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>89</v>
@@ -2781,7 +2781,7 @@
         <v>28</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.8587</v>
+        <v>3.8628</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>18</v>
@@ -2814,7 +2814,7 @@
         <v>0.8912</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.5379</v>
+        <v>0.5384</v>
       </c>
       <c r="T6" s="3" t="s">
         <v>89</v>
@@ -2849,7 +2849,7 @@
         <v>26</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.1523</v>
+        <v>4.1543</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>6</v>
@@ -2882,7 +2882,7 @@
         <v>0.82</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.5487</v>
+        <v>0.549</v>
       </c>
       <c r="T7" s="3" t="s">
         <v>89</v>
@@ -2917,7 +2917,7 @@
         <v>26</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.1523</v>
+        <v>4.1543</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>9</v>
@@ -2950,7 +2950,7 @@
         <v>0.3737</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.1343</v>
+        <v>0.1344</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>92</v>
@@ -2985,7 +2985,7 @@
         <v>26</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.1523</v>
+        <v>4.1543</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>12</v>
@@ -3018,7 +3018,7 @@
         <v>0.8224</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.3522</v>
+        <v>0.3524</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>89</v>
@@ -3053,7 +3053,7 @@
         <v>26</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.1523</v>
+        <v>4.1543</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
@@ -3086,7 +3086,7 @@
         <v>1.3403</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.5216</v>
+        <v>0.5218</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>95</v>
@@ -3121,7 +3121,7 @@
         <v>26</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.1523</v>
+        <v>4.1543</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>18</v>
@@ -3154,7 +3154,7 @@
         <v>1.7317</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>1.1218</v>
+        <v>1.1223</v>
       </c>
       <c r="T11" s="3" t="s">
         <v>95</v>

--- a/files/NRL_try_channel_matchups.xlsx
+++ b/files/NRL_try_channel_matchups.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
   <si>
     <t xml:space="preserve">date_local</t>
   </si>
@@ -233,6 +233,15 @@
     <t xml:space="preserve">left_centre 1.18 (off 1.12 x def 1.06): Starford To'a; right_centre 1.51 (off 1.31 x def 1.15): Heamasi Makasini</t>
   </si>
   <si>
+    <t xml:space="preserve">gold coast titans v north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fullback 1.19 (off 1.07 x def 1.11): Scott Drinkwater; right_centre 1.44 (off 1.40 x def 1.03): Zac Laybutt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left_wing 1.40 (off 1.23 x def 1.14): Phillip Sami</t>
+  </si>
+  <si>
     <t xml:space="preserve">match_id</t>
   </si>
   <si>
@@ -795,6 +804,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sunia Turuva (last 2026-07-18, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260806-1950-gold-coast-titans-north-queensland-cowboys</t>
   </si>
   <si>
     <t xml:space="preserve">team_name</t>
@@ -2371,8 +2383,144 @@
         <v>71</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="U19" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:S17">
+  <conditionalFormatting sqref="G2:S19">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2426,7 +2574,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -2441,49 +2589,49 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2">
@@ -2494,7 +2642,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>23</v>
@@ -2509,7 +2657,7 @@
         <v>28</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>3.6963</v>
+        <v>3.7272</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>6</v>
@@ -2542,16 +2690,16 @@
         <v>0.9087</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.5335</v>
+        <v>0.5379</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
@@ -2562,7 +2710,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>23</v>
@@ -2577,7 +2725,7 @@
         <v>28</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>3.6963</v>
+        <v>3.7272</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
@@ -2610,16 +2758,16 @@
         <v>0.7214</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.2411</v>
+        <v>0.2431</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4">
@@ -2630,7 +2778,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>23</v>
@@ -2645,7 +2793,7 @@
         <v>28</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>3.6963</v>
+        <v>3.7272</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>12</v>
@@ -2678,16 +2826,16 @@
         <v>1.4365</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.544</v>
+        <v>0.5486</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -2698,7 +2846,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>23</v>
@@ -2713,7 +2861,7 @@
         <v>28</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3.6963</v>
+        <v>3.7272</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
@@ -2746,16 +2894,16 @@
         <v>1.1407</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.3974</v>
+        <v>0.4007</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
@@ -2766,7 +2914,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>23</v>
@@ -2781,7 +2929,7 @@
         <v>28</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.6963</v>
+        <v>3.7272</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>18</v>
@@ -2814,16 +2962,16 @@
         <v>1.0453</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6205</v>
+        <v>0.6257</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -2834,7 +2982,7 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>23</v>
@@ -2849,7 +2997,7 @@
         <v>26</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.2775</v>
+        <v>4.2465</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>6</v>
@@ -2882,16 +3030,16 @@
         <v>1.3489</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.9111</v>
+        <v>0.9045</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8">
@@ -2902,7 +3050,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>23</v>
@@ -2917,7 +3065,7 @@
         <v>26</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.2775</v>
+        <v>4.2465</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>9</v>
@@ -2950,16 +3098,16 @@
         <v>0.9004</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.3462</v>
+        <v>0.3437</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9">
@@ -2970,7 +3118,7 @@
         <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>23</v>
@@ -2985,7 +3133,7 @@
         <v>26</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.2775</v>
+        <v>4.2465</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>12</v>
@@ -3018,16 +3166,16 @@
         <v>0.8462</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.3687</v>
+        <v>0.3661</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -3038,7 +3186,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>23</v>
@@ -3053,7 +3201,7 @@
         <v>26</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.2775</v>
+        <v>4.2465</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
@@ -3086,16 +3234,16 @@
         <v>0.9558</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.3831</v>
+        <v>0.3803</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -3106,7 +3254,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>23</v>
@@ -3121,7 +3269,7 @@
         <v>26</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.2775</v>
+        <v>4.2465</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>18</v>
@@ -3154,16 +3302,16 @@
         <v>1.0706</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.7312</v>
+        <v>0.7259</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12">
@@ -3174,7 +3322,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>31</v>
@@ -3189,7 +3337,7 @@
         <v>26</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.9117</v>
+        <v>4.7905</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>6</v>
@@ -3222,16 +3370,16 @@
         <v>0.8828</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.6848</v>
+        <v>0.6679</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13">
@@ -3242,7 +3390,7 @@
         <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>31</v>
@@ -3257,7 +3405,7 @@
         <v>26</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.9117</v>
+        <v>4.7905</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>9</v>
@@ -3290,16 +3438,16 @@
         <v>1.1688</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.5161</v>
+        <v>0.5034</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -3310,7 +3458,7 @@
         <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>31</v>
@@ -3325,7 +3473,7 @@
         <v>26</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.9117</v>
+        <v>4.7905</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>12</v>
@@ -3358,16 +3506,16 @@
         <v>1.7414</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.8714</v>
+        <v>0.8499</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15">
@@ -3378,7 +3526,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>31</v>
@@ -3393,7 +3541,7 @@
         <v>26</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.9117</v>
+        <v>4.7905</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>15</v>
@@ -3426,16 +3574,16 @@
         <v>1.0338</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.4758</v>
+        <v>0.464</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16">
@@ -3446,7 +3594,7 @@
         <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>31</v>
@@ -3461,7 +3609,7 @@
         <v>26</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.9117</v>
+        <v>4.7905</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>18</v>
@@ -3494,16 +3642,16 @@
         <v>0.8971</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.7035</v>
+        <v>0.6862</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
@@ -3514,7 +3662,7 @@
         <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>31</v>
@@ -3529,7 +3677,7 @@
         <v>28</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.2453</v>
+        <v>3.3892</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>6</v>
@@ -3562,16 +3710,16 @@
         <v>1.1623</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.6016</v>
+        <v>0.6283</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
@@ -3582,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>31</v>
@@ -3597,7 +3745,7 @@
         <v>28</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.2453</v>
+        <v>3.3892</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>9</v>
@@ -3630,16 +3778,16 @@
         <v>1.2448</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.3668</v>
+        <v>0.3831</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19">
@@ -3650,7 +3798,7 @@
         <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>31</v>
@@ -3665,7 +3813,7 @@
         <v>28</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.2453</v>
+        <v>3.3892</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>12</v>
@@ -3698,16 +3846,16 @@
         <v>1.039</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.347</v>
+        <v>0.3624</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20">
@@ -3718,7 +3866,7 @@
         <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>31</v>
@@ -3733,7 +3881,7 @@
         <v>28</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.2453</v>
+        <v>3.3892</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>15</v>
@@ -3766,16 +3914,16 @@
         <v>0.6769</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.2079</v>
+        <v>0.2171</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21">
@@ -3786,7 +3934,7 @@
         <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>31</v>
@@ -3801,7 +3949,7 @@
         <v>28</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.2453</v>
+        <v>3.3892</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>18</v>
@@ -3834,16 +3982,16 @@
         <v>0.9112</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.4769</v>
+        <v>0.4981</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22">
@@ -3854,7 +4002,7 @@
         <v>36</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>37</v>
@@ -3869,7 +4017,7 @@
         <v>26</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.8729</v>
+        <v>2.867</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>6</v>
@@ -3902,16 +4050,16 @@
         <v>1.0464</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.4701</v>
+        <v>0.4692</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23">
@@ -3922,7 +4070,7 @@
         <v>36</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>37</v>
@@ -3937,7 +4085,7 @@
         <v>26</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.8729</v>
+        <v>2.867</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>9</v>
@@ -3970,16 +4118,16 @@
         <v>1.0313</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.2638</v>
+        <v>0.2632</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24">
@@ -3990,7 +4138,7 @@
         <v>36</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>37</v>
@@ -4005,7 +4153,7 @@
         <v>26</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.8729</v>
+        <v>2.867</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>12</v>
@@ -4038,16 +4186,16 @@
         <v>0.5747</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.1666</v>
+        <v>0.1662</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25">
@@ -4058,7 +4206,7 @@
         <v>36</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>37</v>
@@ -4073,7 +4221,7 @@
         <v>26</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.8729</v>
+        <v>2.867</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>15</v>
@@ -4106,16 +4254,16 @@
         <v>0.8872</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.2365</v>
+        <v>0.236</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26">
@@ -4126,7 +4274,7 @@
         <v>36</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>37</v>
@@ -4141,7 +4289,7 @@
         <v>26</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.8729</v>
+        <v>2.867</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>18</v>
@@ -4174,16 +4322,16 @@
         <v>1.0264</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.4662</v>
+        <v>0.4653</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27">
@@ -4194,7 +4342,7 @@
         <v>36</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>37</v>
@@ -4209,7 +4357,7 @@
         <v>28</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.2156</v>
+        <v>4.2215</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>6</v>
@@ -4242,16 +4390,16 @@
         <v>1.1829</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.7628</v>
+        <v>0.7639</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28">
@@ -4262,7 +4410,7 @@
         <v>36</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>37</v>
@@ -4277,7 +4425,7 @@
         <v>28</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.2156</v>
+        <v>4.2215</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>9</v>
@@ -4310,16 +4458,16 @@
         <v>0.4276</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.157</v>
+        <v>0.1572</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29">
@@ -4330,7 +4478,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>37</v>
@@ -4345,7 +4493,7 @@
         <v>28</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.2156</v>
+        <v>4.2215</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>12</v>
@@ -4378,16 +4526,16 @@
         <v>1.0074</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.4191</v>
+        <v>0.4196</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30">
@@ -4398,7 +4546,7 @@
         <v>36</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>37</v>
@@ -4413,7 +4561,7 @@
         <v>28</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.2156</v>
+        <v>4.2215</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>15</v>
@@ -4446,16 +4594,16 @@
         <v>0.3919</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.15</v>
+        <v>0.1502</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31">
@@ -4466,7 +4614,7 @@
         <v>36</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>37</v>
@@ -4481,7 +4629,7 @@
         <v>28</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.2156</v>
+        <v>4.2215</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>18</v>
@@ -4514,16 +4662,16 @@
         <v>1.3173</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.8589</v>
+        <v>0.8601</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32">
@@ -4534,7 +4682,7 @@
         <v>42</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>43</v>
@@ -4585,13 +4733,13 @@
         <v>0.7153</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33">
@@ -4602,7 +4750,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>43</v>
@@ -4653,13 +4801,13 @@
         <v>0.477</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34">
@@ -4670,7 +4818,7 @@
         <v>42</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>43</v>
@@ -4721,13 +4869,13 @@
         <v>0.2497</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35">
@@ -4738,7 +4886,7 @@
         <v>42</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>43</v>
@@ -4789,13 +4937,13 @@
         <v>0.3107</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36">
@@ -4806,7 +4954,7 @@
         <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>43</v>
@@ -4857,13 +5005,13 @@
         <v>0.4174</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37">
@@ -4874,7 +5022,7 @@
         <v>42</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>43</v>
@@ -4925,13 +5073,13 @@
         <v>0.773</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38">
@@ -4942,7 +5090,7 @@
         <v>42</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>43</v>
@@ -4993,13 +5141,13 @@
         <v>0.1946</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39">
@@ -5010,7 +5158,7 @@
         <v>42</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>43</v>
@@ -5061,13 +5209,13 @@
         <v>0.2335</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40">
@@ -5078,7 +5226,7 @@
         <v>42</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>43</v>
@@ -5129,13 +5277,13 @@
         <v>0.3986</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41">
@@ -5146,7 +5294,7 @@
         <v>42</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>43</v>
@@ -5197,13 +5345,13 @@
         <v>0.6663</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42">
@@ -5214,7 +5362,7 @@
         <v>48</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -5265,13 +5413,13 @@
         <v>0.384</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43">
@@ -5282,7 +5430,7 @@
         <v>48</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
@@ -5333,13 +5481,13 @@
         <v>0.19</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="V43" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44">
@@ -5350,7 +5498,7 @@
         <v>48</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
@@ -5401,13 +5549,13 @@
         <v>0.2819</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45">
@@ -5418,7 +5566,7 @@
         <v>48</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
@@ -5469,13 +5617,13 @@
         <v>0.3625</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46">
@@ -5486,7 +5634,7 @@
         <v>48</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
@@ -5537,13 +5685,13 @@
         <v>0.27</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47">
@@ -5554,7 +5702,7 @@
         <v>48</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>49</v>
@@ -5605,13 +5753,13 @@
         <v>0.7922</v>
       </c>
       <c r="T47" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48">
@@ -5622,7 +5770,7 @@
         <v>48</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
@@ -5673,13 +5821,13 @@
         <v>0.7969</v>
       </c>
       <c r="T48" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49">
@@ -5690,7 +5838,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>49</v>
@@ -5741,13 +5889,13 @@
         <v>0.2659</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50">
@@ -5758,7 +5906,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
@@ -5809,13 +5957,13 @@
         <v>0.3418</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="51">
@@ -5826,7 +5974,7 @@
         <v>48</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>49</v>
@@ -5877,13 +6025,13 @@
         <v>0.8058</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52">
@@ -5894,7 +6042,7 @@
         <v>54</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>55</v>
@@ -5909,7 +6057,7 @@
         <v>28</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>4.3166</v>
+        <v>4.33</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>6</v>
@@ -5942,16 +6090,16 @@
         <v>0.8943</v>
       </c>
       <c r="S52" s="4" t="n">
-        <v>0.601</v>
+        <v>0.6028</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="53">
@@ -5962,7 +6110,7 @@
         <v>54</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>55</v>
@@ -5977,7 +6125,7 @@
         <v>28</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>4.3166</v>
+        <v>4.33</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>9</v>
@@ -6010,16 +6158,16 @@
         <v>1.0346</v>
       </c>
       <c r="S53" s="4" t="n">
-        <v>0.3958</v>
+        <v>0.3971</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54">
@@ -6030,7 +6178,7 @@
         <v>54</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>55</v>
@@ -6045,7 +6193,7 @@
         <v>28</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>4.3166</v>
+        <v>4.33</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>12</v>
@@ -6078,16 +6226,16 @@
         <v>1.1957</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>0.5184</v>
+        <v>0.52</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="V54" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55">
@@ -6098,7 +6246,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>55</v>
@@ -6113,7 +6261,7 @@
         <v>28</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>4.3166</v>
+        <v>4.33</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>15</v>
@@ -6146,16 +6294,16 @@
         <v>1.5151</v>
       </c>
       <c r="S55" s="4" t="n">
-        <v>0.6041</v>
+        <v>0.606</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="56">
@@ -6166,7 +6314,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>55</v>
@@ -6181,7 +6329,7 @@
         <v>28</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>4.3166</v>
+        <v>4.33</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>18</v>
@@ -6214,16 +6362,16 @@
         <v>0.5119</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>0.3478</v>
+        <v>0.3489</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="57">
@@ -6234,7 +6382,7 @@
         <v>54</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>55</v>
@@ -6249,7 +6397,7 @@
         <v>26</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>3.4815</v>
+        <v>3.4949</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>6</v>
@@ -6282,16 +6430,16 @@
         <v>0.7528</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>0.4125</v>
+        <v>0.4141</v>
       </c>
       <c r="T57" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="V57" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58">
@@ -6302,7 +6450,7 @@
         <v>54</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>55</v>
@@ -6317,7 +6465,7 @@
         <v>26</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>3.4815</v>
+        <v>3.4949</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>9</v>
@@ -6350,16 +6498,16 @@
         <v>1.2122</v>
       </c>
       <c r="S58" s="4" t="n">
-        <v>0.3781</v>
+        <v>0.3796</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="V58" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59">
@@ -6370,7 +6518,7 @@
         <v>54</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>55</v>
@@ -6385,7 +6533,7 @@
         <v>26</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>3.4815</v>
+        <v>3.4949</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>12</v>
@@ -6418,16 +6566,16 @@
         <v>1.0598</v>
       </c>
       <c r="S59" s="4" t="n">
-        <v>0.3746</v>
+        <v>0.3761</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="V59" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60">
@@ -6438,7 +6586,7 @@
         <v>54</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>55</v>
@@ -6453,7 +6601,7 @@
         <v>26</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>3.4815</v>
+        <v>3.4949</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>15</v>
@@ -6486,16 +6634,16 @@
         <v>0.6093</v>
       </c>
       <c r="S60" s="4" t="n">
-        <v>0.1981</v>
+        <v>0.1989</v>
       </c>
       <c r="T60" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="V60" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="61">
@@ -6506,7 +6654,7 @@
         <v>54</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>55</v>
@@ -6521,7 +6669,7 @@
         <v>26</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>3.4815</v>
+        <v>3.4949</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>18</v>
@@ -6554,16 +6702,16 @@
         <v>1.3939</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>0.7723</v>
+        <v>0.7752</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="V61" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="62">
@@ -6574,7 +6722,7 @@
         <v>60</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>61</v>
@@ -6625,13 +6773,13 @@
         <v>0.6581</v>
       </c>
       <c r="T62" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63">
@@ -6642,7 +6790,7 @@
         <v>60</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>61</v>
@@ -6693,13 +6841,13 @@
         <v>0.5581</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="64">
@@ -6710,7 +6858,7 @@
         <v>60</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>61</v>
@@ -6761,13 +6909,13 @@
         <v>0.4824</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="V64" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="65">
@@ -6778,7 +6926,7 @@
         <v>60</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>61</v>
@@ -6829,13 +6977,13 @@
         <v>0.2208</v>
       </c>
       <c r="T65" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="V65" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66">
@@ -6846,7 +6994,7 @@
         <v>60</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>61</v>
@@ -6897,13 +7045,13 @@
         <v>0.6627</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67">
@@ -6914,7 +7062,7 @@
         <v>60</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>61</v>
@@ -6965,13 +7113,13 @@
         <v>0.4181</v>
       </c>
       <c r="T67" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="68">
@@ -6982,7 +7130,7 @@
         <v>60</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>61</v>
@@ -7033,13 +7181,13 @@
         <v>0.125</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="V68" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="69">
@@ -7050,7 +7198,7 @@
         <v>60</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>61</v>
@@ -7101,13 +7249,13 @@
         <v>0.2781</v>
       </c>
       <c r="T69" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U69" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="V69" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="70">
@@ -7118,7 +7266,7 @@
         <v>60</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>61</v>
@@ -7169,13 +7317,13 @@
         <v>0.5085</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="V70" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71">
@@ -7186,7 +7334,7 @@
         <v>60</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>61</v>
@@ -7237,13 +7385,13 @@
         <v>0.9651</v>
       </c>
       <c r="T71" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U71" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="V71" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72">
@@ -7254,7 +7402,7 @@
         <v>66</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>67</v>
@@ -7269,7 +7417,7 @@
         <v>26</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>4.2089</v>
+        <v>4.2159</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>6</v>
@@ -7302,16 +7450,16 @@
         <v>0.7244</v>
       </c>
       <c r="S72" s="4" t="n">
-        <v>0.4755</v>
+        <v>0.4763</v>
       </c>
       <c r="T72" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U72" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="V72" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73">
@@ -7322,7 +7470,7 @@
         <v>66</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>67</v>
@@ -7337,7 +7485,7 @@
         <v>26</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>4.2089</v>
+        <v>4.2159</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>9</v>
@@ -7370,16 +7518,16 @@
         <v>0.6364</v>
       </c>
       <c r="S73" s="4" t="n">
-        <v>0.2378</v>
+        <v>0.2382</v>
       </c>
       <c r="T73" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U73" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="V73" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74">
@@ -7390,7 +7538,7 @@
         <v>66</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>67</v>
@@ -7405,7 +7553,7 @@
         <v>26</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>4.2089</v>
+        <v>4.2159</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>12</v>
@@ -7438,16 +7586,16 @@
         <v>1.4571</v>
       </c>
       <c r="S74" s="4" t="n">
-        <v>0.617</v>
+        <v>0.618</v>
       </c>
       <c r="T74" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U74" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="V74" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75">
@@ -7458,7 +7606,7 @@
         <v>66</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>67</v>
@@ -7473,7 +7621,7 @@
         <v>26</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>4.2089</v>
+        <v>4.2159</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>15</v>
@@ -7506,16 +7654,16 @@
         <v>1.0529</v>
       </c>
       <c r="S75" s="4" t="n">
-        <v>0.4101</v>
+        <v>0.4108</v>
       </c>
       <c r="T75" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U75" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="V75" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76">
@@ -7526,7 +7674,7 @@
         <v>66</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>67</v>
@@ -7541,7 +7689,7 @@
         <v>26</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>4.2089</v>
+        <v>4.2159</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>18</v>
@@ -7574,16 +7722,16 @@
         <v>1.0309</v>
       </c>
       <c r="S76" s="4" t="n">
-        <v>0.6842</v>
+        <v>0.6853</v>
       </c>
       <c r="T76" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U76" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="V76" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77">
@@ -7594,7 +7742,7 @@
         <v>66</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>67</v>
@@ -7609,7 +7757,7 @@
         <v>28</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>3.8315</v>
+        <v>3.8385</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>6</v>
@@ -7642,16 +7790,16 @@
         <v>0.9966</v>
       </c>
       <c r="S77" s="4" t="n">
-        <v>0.6047</v>
+        <v>0.6058</v>
       </c>
       <c r="T77" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U77" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="V77" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="78">
@@ -7662,7 +7810,7 @@
         <v>66</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>67</v>
@@ -7677,7 +7825,7 @@
         <v>28</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>3.8315</v>
+        <v>3.8385</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>9</v>
@@ -7710,16 +7858,16 @@
         <v>1.1796</v>
       </c>
       <c r="S78" s="4" t="n">
-        <v>0.4074</v>
+        <v>0.4082</v>
       </c>
       <c r="T78" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U78" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="V78" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79">
@@ -7730,7 +7878,7 @@
         <v>66</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>67</v>
@@ -7745,7 +7893,7 @@
         <v>28</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>3.8315</v>
+        <v>3.8385</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>12</v>
@@ -7778,16 +7926,16 @@
         <v>0.812</v>
       </c>
       <c r="S79" s="4" t="n">
-        <v>0.3178</v>
+        <v>0.3184</v>
       </c>
       <c r="T79" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U79" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="V79" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80">
@@ -7798,7 +7946,7 @@
         <v>66</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>67</v>
@@ -7813,7 +7961,7 @@
         <v>28</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>3.8315</v>
+        <v>3.8385</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>15</v>
@@ -7846,16 +7994,16 @@
         <v>1.506</v>
       </c>
       <c r="S80" s="4" t="n">
-        <v>0.5421</v>
+        <v>0.5431</v>
       </c>
       <c r="T80" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U80" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="V80" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="81">
@@ -7866,7 +8014,7 @@
         <v>66</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>67</v>
@@ -7881,7 +8029,7 @@
         <v>28</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>3.8315</v>
+        <v>3.8385</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>18</v>
@@ -7914,16 +8062,696 @@
         <v>0.8268</v>
       </c>
       <c r="S81" s="4" t="n">
-        <v>0.5072</v>
+        <v>0.5081</v>
       </c>
       <c r="T81" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U81" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V81" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>0.1943</v>
+      </c>
+      <c r="M82" s="4" t="n">
+        <v>1.2334</v>
+      </c>
+      <c r="N82" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="O82" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>0.1791</v>
+      </c>
+      <c r="Q82" s="4" t="n">
+        <v>1.1371</v>
+      </c>
+      <c r="R82" s="4" t="n">
+        <v>1.4025</v>
+      </c>
+      <c r="S82" s="4" t="n">
+        <v>0.8895</v>
+      </c>
+      <c r="T82" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="U82" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="V82" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J83" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K83" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>0.0874</v>
+      </c>
+      <c r="M83" s="4" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="N83" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="O83" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="P83" s="4" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="Q83" s="4" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="R83" s="4" t="n">
+        <v>0.9591</v>
+      </c>
+      <c r="S83" s="4" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K84" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="L84" s="4" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="M84" s="4" t="n">
+        <v>0.7133</v>
+      </c>
+      <c r="N84" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="O84" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="P84" s="4" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="Q84" s="4" t="n">
+        <v>0.8354</v>
+      </c>
+      <c r="R84" s="4" t="n">
+        <v>0.5959</v>
+      </c>
+      <c r="S84" s="4" t="n">
+        <v>0.2438</v>
+      </c>
+      <c r="T84" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="U84" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="V84" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J85" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K85" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="L85" s="4" t="n">
+        <v>0.0931</v>
+      </c>
+      <c r="M85" s="4" t="n">
+        <v>0.9958</v>
+      </c>
+      <c r="N85" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="O85" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="P85" s="4" t="n">
+        <v>0.0885</v>
+      </c>
+      <c r="Q85" s="4" t="n">
+        <v>0.9466</v>
+      </c>
+      <c r="R85" s="4" t="n">
+        <v>0.9426</v>
+      </c>
+      <c r="S85" s="4" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="T85" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="U85" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="V85" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K86" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="M86" s="4" t="n">
+        <v>0.9536</v>
+      </c>
+      <c r="N86" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="O86" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="P86" s="4" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="Q86" s="4" t="n">
+        <v>0.8928</v>
+      </c>
+      <c r="R86" s="4" t="n">
+        <v>0.8514</v>
+      </c>
+      <c r="S86" s="4" t="n">
+        <v>0.5459</v>
+      </c>
+      <c r="T86" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="U86" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="V86" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>4.2102</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J87" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="K87" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>0.1793</v>
+      </c>
+      <c r="M87" s="4" t="n">
+        <v>1.1384</v>
+      </c>
+      <c r="N87" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="O87" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="P87" s="4" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="Q87" s="4" t="n">
+        <v>0.9629</v>
+      </c>
+      <c r="R87" s="4" t="n">
+        <v>1.0962</v>
+      </c>
+      <c r="S87" s="4" t="n">
+        <v>0.7293</v>
+      </c>
+      <c r="T87" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="U87" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="V87" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>4.2102</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K88" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="L88" s="4" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="M88" s="4" t="n">
+        <v>0.7123</v>
+      </c>
+      <c r="N88" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="O88" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="P88" s="4" t="n">
+        <v>0.0844</v>
+      </c>
+      <c r="Q88" s="4" t="n">
+        <v>0.9411</v>
+      </c>
+      <c r="R88" s="4" t="n">
+        <v>0.6704</v>
+      </c>
+      <c r="S88" s="4" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="T88" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="U88" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="V88" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>4.2102</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J89" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K89" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="L89" s="4" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="M89" s="4" t="n">
+        <v>1.0725</v>
+      </c>
+      <c r="N89" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="O89" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="P89" s="4" t="n">
+        <v>0.1127</v>
+      </c>
+      <c r="Q89" s="4" t="n">
+        <v>1.1092</v>
+      </c>
+      <c r="R89" s="4" t="n">
+        <v>1.1896</v>
+      </c>
+      <c r="S89" s="4" t="n">
+        <v>0.5106</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>4.2102</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K90" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="L90" s="4" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="M90" s="4" t="n">
+        <v>1.3966</v>
+      </c>
+      <c r="N90" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O90" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="P90" s="4" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="Q90" s="4" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="R90" s="4" t="n">
+        <v>1.4412</v>
+      </c>
+      <c r="S90" s="4" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="T90" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="U90" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="V90" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>4.2102</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J91" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K91" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="L91" s="4" t="n">
+        <v>0.1706</v>
+      </c>
+      <c r="M91" s="4" t="n">
+        <v>1.0711</v>
+      </c>
+      <c r="N91" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="O91" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="P91" s="4" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="Q91" s="4" t="n">
+        <v>1.0025</v>
+      </c>
+      <c r="R91" s="4" t="n">
+        <v>1.0738</v>
+      </c>
+      <c r="S91" s="4" t="n">
+        <v>0.7223</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -7951,34 +8779,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2">
@@ -8943,7 +9771,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>6</v>
@@ -8975,7 +9803,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>9</v>
@@ -9007,7 +9835,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>12</v>
@@ -9039,7 +9867,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>15</v>
@@ -9071,7 +9899,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>18</v>
@@ -10718,42 +11546,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6">
@@ -10761,23 +11589,23 @@
         <v>21</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_try_channel_matchups.xlsx
+++ b/files/NRL_try_channel_matchups.xlsx
@@ -98,13 +98,13 @@
     <t xml:space="preserve">away</t>
   </si>
   <si>
-    <t xml:space="preserve">right_centre 1.58 (off 1.28 x def 1.24): Tallis Duncan; right_wing 1.76 (off 1.52 x def 1.16): Alex Johnston</t>
+    <t xml:space="preserve">right_centre 1.59 (off 1.28 x def 1.24): Tallis Duncan; right_wing 1.78 (off 1.53 x def 1.17): Alex Johnston</t>
   </si>
   <si>
     <t xml:space="preserve">home</t>
   </si>
   <si>
-    <t xml:space="preserve">left_centre 1.27 (off 1.53 x def 0.83): KL Iro</t>
+    <t xml:space="preserve">left_centre 1.20 (off 1.51 x def 0.80): KL Iro</t>
   </si>
   <si>
     <t xml:space="preserve">16:05</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">fullback 1.44 (off 1.20 x def 1.20): Isaiah Iongi</t>
   </si>
   <si>
-    <t xml:space="preserve">left_centre 1.22 (off 1.15 x def 1.07): Starford To'a; right_centre 1.51 (off 1.29 x def 1.17): Heamasi Makasini</t>
+    <t xml:space="preserve">left_centre 1.22 (off 1.15 x def 1.07): Starford To'a; right_centre 1.50 (off 1.29 x def 1.17): Heamasi Makasini</t>
   </si>
   <si>
     <t xml:space="preserve">19:50</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">gold coast titans</t>
   </si>
   <si>
-    <t xml:space="preserve">right_centre 1.45 (off 1.40 x def 1.04): Zac Laybutt</t>
+    <t xml:space="preserve">right_centre 1.45 (off 1.39 x def 1.04): Zac Laybutt</t>
   </si>
   <si>
     <t xml:space="preserve">left_wing 1.39 (off 1.19 x def 1.17): Phillip Sami</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">No wing/centre/fullback focus &gt;= 1.12</t>
   </si>
   <si>
-    <t xml:space="preserve">left_wing 1.68 (off 1.22 x def 1.38): Mark Nawaqanitawase; right_wing 1.59 (off 1.20 x def 1.33): Daniel Tupou</t>
+    <t xml:space="preserve">left_wing 1.68 (off 1.22 x def 1.38): Mark Nawaqanitawase; right_wing 1.60 (off 1.20 x def 1.33): Daniel Tupou</t>
   </si>
   <si>
     <t xml:space="preserve">warriors v penrith panthers</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">left_wing 1.12 (off 0.96 x def 1.17): Brian To'o; left_centre 2.25 (off 1.36 x def 1.65): Casey McLean</t>
+    <t xml:space="preserve">left_wing 1.12 (off 0.96 x def 1.17): Brian To'o; left_centre 2.26 (off 1.37 x def 1.65): Casey McLean</t>
   </si>
   <si>
     <t xml:space="preserve">left_wing 1.25 (off 1.20 x def 1.04): Alofiana Khan-Pereira; right_centre 1.12 (off 0.99 x def 1.13): Ali Leiataua</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">melbourne storm</t>
   </si>
   <si>
-    <t xml:space="preserve">left_wing 1.15 (off 1.06 x def 1.08): Lehi Hopoate; left_centre 1.22 (off 1.03 x def 1.19): Reuben Garrick; right_centre 1.42 (off 1.51 x def 0.94): Tolutau Koula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fullback 1.23 (off 1.41 x def 0.87): Sualauvi Faalogo</t>
+    <t xml:space="preserve">left_wing 1.15 (off 1.07 x def 1.08): Lehi Hopoate; left_centre 1.23 (off 1.03 x def 1.19): Reuben Garrick; right_centre 1.42 (off 1.51 x def 0.94): Tolutau Koula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fullback 1.23 (off 1.42 x def 0.87): Sualauvi Faalogo</t>
   </si>
   <si>
     <t xml:space="preserve">17:30</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">left_centre 1.35 (off 1.36 x def 1.00): Gehamat Shibasaki; right_centre 1.35 (off 1.22 x def 1.11): Kotoni Staggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_centre 1.71 (off 1.47 x def 1.16): Herbie Farnworth; fullback 1.60 (off 1.51 x def 1.06): Hamiso Tabuai-Fidow</t>
+    <t xml:space="preserve">left_centre 1.36 (off 1.36 x def 1.00): Gehamat Shibasaki; right_centre 1.35 (off 1.21 x def 1.11): Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left_centre 1.71 (off 1.48 x def 1.16): Herbie Farnworth; fullback 1.61 (off 1.52 x def 1.06): Hamiso Tabuai-Fidow</t>
   </si>
   <si>
     <t xml:space="preserve">19:35</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">south sydney rabbitohs v parramatta eels</t>
   </si>
   <si>
-    <t xml:space="preserve">fullback 1.68 (off 1.20 x def 1.40): Isaiah Iongi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">right_centre 1.49 (off 1.28 x def 1.17): Tallis Duncan; right_wing 1.62 (off 1.52 x def 1.06): Alex Johnston</t>
+    <t xml:space="preserve">fullback 1.71 (off 1.20 x def 1.43): Isaiah Iongi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">right_centre 1.50 (off 1.28 x def 1.17): Tallis Duncan; right_wing 1.63 (off 1.53 x def 1.06): Alex Johnston</t>
   </si>
   <si>
     <t xml:space="preserve">canberra raiders v newcastle knights</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">canberra raiders</t>
   </si>
   <si>
-    <t xml:space="preserve">left_wing 1.16 (off 1.00 x def 1.16): Greg Marzhew; left_centre 1.45 (off 1.03 x def 1.42): Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">right_centre 1.54 (off 1.23 x def 1.26): Simi Sasagi</t>
+    <t xml:space="preserve">left_wing 1.16 (off 1.00 x def 1.16): Greg Marzhew; left_centre 1.46 (off 1.03 x def 1.42): Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">right_centre 1.54 (off 1.22 x def 1.26): Simi Sasagi</t>
   </si>
   <si>
     <t xml:space="preserve">st george-illawarra dragons v cronulla-sutherland sharks</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">st george-illawarra dragons</t>
   </si>
   <si>
-    <t xml:space="preserve">left_centre 1.24 (off 1.53 x def 0.81): KL Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_wing 1.22 (off 1.20 x def 1.02): Tyrell Sloan; right_wing 1.24 (off 1.07 x def 1.16): Setu Tu</t>
+    <t xml:space="preserve">left_centre 1.22 (off 1.51 x def 0.81): KL Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left_wing 1.23 (off 1.20 x def 1.02): Tyrell Sloan; right_wing 1.25 (off 1.07 x def 1.17): Setu Tu</t>
   </si>
   <si>
     <t xml:space="preserve">match_id</t>
@@ -1354,34 +1354,34 @@
         <v>26</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>1.02</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0.48</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="M2" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O2" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="N2" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="O2" s="4" t="n">
-        <v>0.87</v>
-      </c>
       <c r="P2" s="4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q2" s="4" t="n">
         <v>1.28</v>
@@ -1390,13 +1390,13 @@
         <v>1.24</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="V2" s="3" t="s">
         <v>27</v>
@@ -1422,49 +1422,49 @@
         <v>28</v>
       </c>
       <c r="G3" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="H3" s="4" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0.89</v>
-      </c>
       <c r="J3" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="L3" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="T3" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="M3" s="4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>0.85</v>
-      </c>
       <c r="U3" s="4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>29</v>
@@ -1517,7 +1517,7 @@
         <v>1.2</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Q4" s="4" t="n">
         <v>1.21</v>
@@ -1585,7 +1585,7 @@
         <v>0.76</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" s="4" t="n">
         <v>1.29</v>
@@ -1641,7 +1641,7 @@
         <v>0.73</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>1.11</v>
@@ -1650,13 +1650,13 @@
         <v>1.04</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>1.45</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>1.04</v>
@@ -1703,10 +1703,10 @@
         <v>1.17</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>1</v>
@@ -1771,7 +1771,7 @@
         <v>0.79</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>0.87</v>
@@ -1795,7 +1795,7 @@
         <v>0.95</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="S8" s="4" t="n">
         <v>0.79</v>
@@ -1866,7 +1866,7 @@
         <v>0.79</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>1.2</v>
@@ -1907,10 +1907,10 @@
         <v>1.17</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>1.65</v>
@@ -1922,16 +1922,16 @@
         <v>0.85</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>0.86</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="S10" s="4" t="n">
         <v>1.08</v>
@@ -1975,7 +1975,7 @@
         <v>1.04</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0.55</v>
@@ -2037,13 +2037,13 @@
         <v>1.15</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>1.08</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>1.03</v>
@@ -2123,7 +2123,7 @@
         <v>1.23</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="O13" s="4" t="n">
         <v>0.87</v>
@@ -2138,7 +2138,7 @@
         <v>0.66</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>1</v>
@@ -2179,7 +2179,7 @@
         <v>1.02</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>1.36</v>
@@ -2188,7 +2188,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>1.1</v>
@@ -2200,7 +2200,7 @@
         <v>1.35</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>1.11</v>
@@ -2250,16 +2250,16 @@
         <v>1.71</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>1.16</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="O15" s="4" t="n">
         <v>1.06</v>
@@ -2306,49 +2306,49 @@
         <v>26</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0.95</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>0.58</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>1.21</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.97</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V16" s="3" t="s">
         <v>67</v>
@@ -2377,7 +2377,7 @@
         <v>0.74</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>0.97</v>
@@ -2392,16 +2392,16 @@
         <v>1.07</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.72</v>
+        <v>0.69</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="O17" s="4" t="n">
         <v>0.76</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>1.28</v>
@@ -2410,10 +2410,10 @@
         <v>1.17</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U17" s="4" t="n">
         <v>1.06</v>
@@ -2451,7 +2451,7 @@
         <v>1.16</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>1.03</v>
@@ -2475,7 +2475,7 @@
         <v>0.54</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="S18" s="4" t="n">
         <v>1.05</v>
@@ -2510,7 +2510,7 @@
         <v>28</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>0.85</v>
@@ -2540,7 +2540,7 @@
         <v>1.54</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R19" s="4" t="n">
         <v>1.26</v>
@@ -2578,46 +2578,46 @@
         <v>26</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>1.05</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>0.81</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="O20" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="R20" s="4" t="n">
         <v>1.09</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>1.04</v>
@@ -2646,7 +2646,7 @@
         <v>28</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>1.2</v>
@@ -2655,22 +2655,22 @@
         <v>1.02</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>1.29</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>1.12</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>0.75</v>
@@ -2682,13 +2682,13 @@
         <v>1.24</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>1.07</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>77</v>
@@ -2832,40 +2832,40 @@
         <v>28</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>4.9046</v>
+        <v>4.656</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.1544</v>
+        <v>0.1528</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.9816</v>
+        <v>0.9723</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.1393</v>
+        <v>0.1373</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.8861</v>
+        <v>0.8733</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.8698</v>
+        <v>0.8491</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.6768</v>
+        <v>0.6286</v>
       </c>
       <c r="T2" s="3" t="s">
         <v>95</v>
@@ -2900,40 +2900,40 @@
         <v>28</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>4.9046</v>
+        <v>4.656</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.1385</v>
+        <v>0.1367</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>1.5308</v>
+        <v>1.5138</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.0751</v>
+        <v>0.0718</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>0.8303</v>
+        <v>0.7956</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>1.271</v>
+        <v>1.2044</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.5688</v>
+        <v>0.5122</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>98</v>
@@ -2968,7 +2968,7 @@
         <v>28</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>4.9046</v>
+        <v>4.656</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>12</v>
@@ -2977,31 +2977,31 @@
         <v>17</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0726</v>
+        <v>0.0738</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.7291</v>
+        <v>0.7417</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>29</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.1397</v>
+        <v>0.1423</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>1.4024</v>
+        <v>1.4305</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1.0225</v>
+        <v>1.061</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.504</v>
+        <v>0.497</v>
       </c>
       <c r="T4" s="3" t="s">
         <v>95</v>
@@ -3036,7 +3036,7 @@
         <v>28</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>4.9046</v>
+        <v>4.656</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
@@ -3045,31 +3045,31 @@
         <v>14</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.0605</v>
+        <v>0.0615</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.6461</v>
+        <v>0.6555</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>14</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.0721</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.7553</v>
+        <v>0.7683</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.488</v>
+        <v>0.5036</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.2263</v>
+        <v>0.2226</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>103</v>
@@ -3104,40 +3104,40 @@
         <v>28</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.9046</v>
+        <v>4.656</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>236</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.8345</v>
+      </c>
+      <c r="N6" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0.8456</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>33</v>
-      </c>
       <c r="O6" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1623</v>
+        <v>0.1607</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1.0171</v>
+        <v>1.0072</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.86</v>
+        <v>0.8405</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6793</v>
+        <v>0.6316</v>
       </c>
       <c r="T6" s="3" t="s">
         <v>95</v>
@@ -3172,7 +3172,7 @@
         <v>26</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.4395</v>
+        <v>3.6882</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>6</v>
@@ -3181,31 +3181,31 @@
         <v>21</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.12</v>
+        <v>0.1206</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.763</v>
+        <v>0.7671</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>30</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1602</v>
+        <v>0.161</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>1.0186</v>
+        <v>1.024</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.7771</v>
+        <v>0.7856</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.4041</v>
+        <v>0.4373</v>
       </c>
       <c r="T7" s="3" t="s">
         <v>95</v>
@@ -3240,7 +3240,7 @@
         <v>26</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.4395</v>
+        <v>3.6882</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>9</v>
@@ -3249,31 +3249,31 @@
         <v>7</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0431</v>
+        <v>0.0433</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4765</v>
+        <v>0.4796</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>14</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.0761</v>
+        <v>0.0765</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.8413</v>
+        <v>0.8468</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.4008</v>
+        <v>0.4062</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.1199</v>
+        <v>0.1299</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>103</v>
@@ -3308,43 +3308,43 @@
         <v>26</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.4395</v>
+        <v>3.6882</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.0949</v>
+        <v>0.0902</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.9523</v>
+        <v>0.907</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.0867</v>
+        <v>0.0821</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.87</v>
+        <v>0.8258</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.8286</v>
+        <v>0.7489</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.2638</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>112</v>
@@ -3376,7 +3376,7 @@
         <v>26</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.4395</v>
+        <v>3.6882</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
@@ -3385,31 +3385,31 @@
         <v>22</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1199</v>
+        <v>0.1205</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.2795</v>
+        <v>1.2843</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>22</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1158</v>
+        <v>0.1163</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.2354</v>
+        <v>1.2398</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.5807</v>
+        <v>1.5922</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.4898</v>
+        <v>0.5291</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>114</v>
@@ -3444,7 +3444,7 @@
         <v>26</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.4395</v>
+        <v>3.6882</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>18</v>
@@ -3453,31 +3453,31 @@
         <v>45</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2426</v>
+        <v>0.2439</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.52</v>
+        <v>1.5283</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>35</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.185</v>
+        <v>0.1859</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.159</v>
+        <v>1.1651</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.7616</v>
+        <v>1.7806</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.9298</v>
+        <v>1.0061</v>
       </c>
       <c r="T11" s="3" t="s">
         <v>114</v>
@@ -3512,7 +3512,7 @@
         <v>26</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.3062</v>
+        <v>4.3784</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>6</v>
@@ -3527,7 +3527,7 @@
         <v>0.1491</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.9479</v>
+        <v>0.9483</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>25</v>
@@ -3539,13 +3539,13 @@
         <v>0.1151</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.7321</v>
+        <v>0.7324</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.694</v>
+        <v>0.6945</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.4669</v>
+        <v>0.4749</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>103</v>
@@ -3580,7 +3580,7 @@
         <v>26</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.3062</v>
+        <v>4.3784</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>9</v>
@@ -3595,7 +3595,7 @@
         <v>0.0528</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5833</v>
+        <v>0.5842</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>21</v>
@@ -3607,13 +3607,13 @@
         <v>0.0939</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.0384</v>
+        <v>1.0401</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.6057</v>
+        <v>0.6077</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.2344</v>
+        <v>0.2387</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>103</v>
@@ -3648,7 +3648,7 @@
         <v>26</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.3062</v>
+        <v>4.3784</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>12</v>
@@ -3660,10 +3660,10 @@
         <v>182</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1192</v>
+        <v>0.1191</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.1962</v>
+        <v>1.1979</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>27</v>
@@ -3675,13 +3675,13 @@
         <v>0.1196</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.201</v>
+        <v>1.2027</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.4367</v>
+        <v>1.4407</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.6122</v>
+        <v>0.6234</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>114</v>
@@ -3716,7 +3716,7 @@
         <v>26</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.3062</v>
+        <v>4.3784</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>15</v>
@@ -3731,7 +3731,7 @@
         <v>0.1136</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.2127</v>
+        <v>1.211</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>18</v>
@@ -3743,13 +3743,13 @@
         <v>0.0816</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.8707</v>
+        <v>0.8695</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.0559</v>
+        <v>1.053</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.4233</v>
+        <v>0.4298</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>95</v>
@@ -3784,7 +3784,7 @@
         <v>26</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.3062</v>
+        <v>4.3784</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>18</v>
@@ -3799,7 +3799,7 @@
         <v>0.1543</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9667</v>
+        <v>0.9671</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>38</v>
@@ -3811,13 +3811,13 @@
         <v>0.1697</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1.063</v>
+        <v>1.0634</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.0277</v>
+        <v>1.0284</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.7018</v>
+        <v>0.7138</v>
       </c>
       <c r="T16" s="3" t="s">
         <v>95</v>
@@ -3852,7 +3852,7 @@
         <v>28</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.7482</v>
+        <v>3.6761</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>6</v>
@@ -3867,7 +3867,7 @@
         <v>0.1658</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.0545</v>
+        <v>1.0548</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>33</v>
@@ -3879,13 +3879,13 @@
         <v>0.1524</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.9693</v>
+        <v>0.9697</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.0221</v>
+        <v>1.0228</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.6028</v>
+        <v>0.5914</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>95</v>
@@ -3920,7 +3920,7 @@
         <v>28</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.7482</v>
+        <v>3.6761</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>9</v>
@@ -3935,7 +3935,7 @@
         <v>0.1036</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.1458</v>
+        <v>1.1477</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>21</v>
@@ -3947,13 +3947,13 @@
         <v>0.0963</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.0651</v>
+        <v>1.0669</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.2203</v>
+        <v>1.2244</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.414</v>
+        <v>0.4067</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>98</v>
@@ -3988,7 +3988,7 @@
         <v>28</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.7482</v>
+        <v>3.6761</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>12</v>
@@ -4003,7 +4003,7 @@
         <v>0.0988</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.9922</v>
+        <v>0.9936</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>16</v>
@@ -4015,13 +4015,13 @@
         <v>0.0755</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.7521</v>
+        <v>0.7542</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.281</v>
+        <v>0.2759</v>
       </c>
       <c r="T19" s="3" t="s">
         <v>95</v>
@@ -4056,7 +4056,7 @@
         <v>28</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.7482</v>
+        <v>3.6761</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>15</v>
@@ -4071,7 +4071,7 @@
         <v>0.1208</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.289</v>
+        <v>1.2872</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>24</v>
@@ -4083,13 +4083,13 @@
         <v>0.1094</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.1679</v>
+        <v>1.1663</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.5054</v>
+        <v>1.5013</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.5291</v>
+        <v>0.5182</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>114</v>
@@ -4124,7 +4124,7 @@
         <v>28</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.7482</v>
+        <v>3.6761</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>18</v>
@@ -4139,7 +4139,7 @@
         <v>0.1211</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7586</v>
+        <v>0.7589</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>37</v>
@@ -4151,13 +4151,13 @@
         <v>0.1698</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.0635</v>
+        <v>1.0639</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.8068</v>
+        <v>0.8073</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.483</v>
+        <v>0.4739</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>95</v>
@@ -4192,7 +4192,7 @@
         <v>28</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>4.081</v>
+        <v>4.146</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>6</v>
@@ -4207,7 +4207,7 @@
         <v>0.1872</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.1907</v>
+        <v>1.1911</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>41</v>
@@ -4219,13 +4219,13 @@
         <v>0.1836</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.1676</v>
+        <v>1.168</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.3902</v>
+        <v>1.3913</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.8769</v>
+        <v>0.8913</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>114</v>
@@ -4260,7 +4260,7 @@
         <v>28</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.081</v>
+        <v>4.146</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>9</v>
@@ -4275,7 +4275,7 @@
         <v>0.0863</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.9541</v>
+        <v>0.9556</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>20</v>
@@ -4287,13 +4287,13 @@
         <v>0.0905</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.0005</v>
+        <v>1.0021</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.9545</v>
+        <v>0.9577</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.3463</v>
+        <v>0.3524</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>95</v>
@@ -4328,7 +4328,7 @@
         <v>28</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4.081</v>
+        <v>4.146</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>12</v>
@@ -4343,7 +4343,7 @@
         <v>0.0648</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6502</v>
+        <v>0.651</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>17</v>
@@ -4352,16 +4352,16 @@
         <v>221</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.0785</v>
+        <v>0.0784</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.7876</v>
+        <v>0.7887</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.5121</v>
+        <v>0.5134</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.2046</v>
+        <v>0.2081</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>103</v>
@@ -4396,7 +4396,7 @@
         <v>28</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.081</v>
+        <v>4.146</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>15</v>
@@ -4411,7 +4411,7 @@
         <v>0.0922</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.9837</v>
+        <v>0.9824</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>19</v>
@@ -4423,13 +4423,13 @@
         <v>0.0865</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.9231</v>
+        <v>0.9218</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.908</v>
+        <v>0.9055</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.3413</v>
+        <v>0.3463</v>
       </c>
       <c r="T25" s="3" t="s">
         <v>95</v>
@@ -4464,7 +4464,7 @@
         <v>28</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.081</v>
+        <v>4.146</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>18</v>
@@ -4479,7 +4479,7 @@
         <v>0.1539</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.9644</v>
+        <v>0.9647</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>31</v>
@@ -4491,13 +4491,13 @@
         <v>0.1416</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.887</v>
+        <v>0.8873</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.8553</v>
+        <v>0.8559</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.5477</v>
+        <v>0.5566</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>95</v>
@@ -4532,7 +4532,7 @@
         <v>26</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.2173</v>
+        <v>4.1522</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>6</v>
@@ -4547,7 +4547,7 @@
         <v>0.1721</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.0943</v>
+        <v>1.0947</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>36</v>
@@ -4556,16 +4556,16 @@
         <v>235</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1535</v>
+        <v>0.1534</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.9758</v>
+        <v>0.9762</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.0679</v>
+        <v>1.0687</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.7103</v>
+        <v>0.6995</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>95</v>
@@ -4600,7 +4600,7 @@
         <v>26</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.2173</v>
+        <v>4.1522</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>9</v>
@@ -4615,7 +4615,7 @@
         <v>0.0663</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.7327</v>
+        <v>0.7339</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>20</v>
@@ -4627,13 +4627,13 @@
         <v>0.0854</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.9447</v>
+        <v>0.9462</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.6921</v>
+        <v>0.6944</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.2648</v>
+        <v>0.2611</v>
       </c>
       <c r="T28" s="3" t="s">
         <v>103</v>
@@ -4668,7 +4668,7 @@
         <v>26</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.2173</v>
+        <v>4.1522</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>12</v>
@@ -4683,7 +4683,7 @@
         <v>0.1036</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.0404</v>
+        <v>1.0419</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>25</v>
@@ -4692,16 +4692,16 @@
         <v>235</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.106</v>
+        <v>0.1059</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1.0636</v>
+        <v>1.0651</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>1.1066</v>
+        <v>1.1097</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.4663</v>
+        <v>0.4596</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>95</v>
@@ -4736,7 +4736,7 @@
         <v>26</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.2173</v>
+        <v>4.1522</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>15</v>
@@ -4751,7 +4751,7 @@
         <v>0.1307</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.3951</v>
+        <v>1.3932</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>23</v>
@@ -4763,13 +4763,13 @@
         <v>0.0976</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.0417</v>
+        <v>1.0402</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.4533</v>
+        <v>1.4492</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.576</v>
+        <v>0.5663</v>
       </c>
       <c r="T30" s="3" t="s">
         <v>114</v>
@@ -4804,7 +4804,7 @@
         <v>26</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.2173</v>
+        <v>4.1522</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>18</v>
@@ -4819,7 +4819,7 @@
         <v>0.1723</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.0792</v>
+        <v>1.0796</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>38</v>
@@ -4831,13 +4831,13 @@
         <v>0.1616</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1.0122</v>
+        <v>1.0126</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>1.0924</v>
+        <v>1.0931</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.7264</v>
       </c>
       <c r="T31" s="3" t="s">
         <v>95</v>
@@ -4872,7 +4872,7 @@
         <v>26</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.6926</v>
+        <v>2.8204</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>6</v>
@@ -4887,7 +4887,7 @@
         <v>0.1549</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.985</v>
+        <v>0.9854</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>22</v>
@@ -4899,13 +4899,13 @@
         <v>0.1238</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.7874</v>
+        <v>0.7877</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.7756</v>
+        <v>0.7762</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.3399</v>
+        <v>0.3561</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>95</v>
@@ -4940,7 +4940,7 @@
         <v>26</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.6926</v>
+        <v>2.8204</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>9</v>
@@ -4955,7 +4955,7 @@
         <v>0.0784</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.8669</v>
+        <v>0.8683</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>17</v>
@@ -4967,13 +4967,13 @@
         <v>0.0932</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>1.03</v>
+        <v>1.0317</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.8929</v>
+        <v>0.8959</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.2251</v>
+        <v>0.2361</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>95</v>
@@ -5008,7 +5008,7 @@
         <v>26</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.6926</v>
+        <v>2.8204</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>12</v>
@@ -5023,7 +5023,7 @@
         <v>0.0639</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.6417</v>
+        <v>0.6426</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>25</v>
@@ -5035,13 +5035,13 @@
         <v>0.1343</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1.3483</v>
+        <v>1.3502</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.8653</v>
+        <v>0.8676</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.2402</v>
+        <v>0.2519</v>
       </c>
       <c r="T34" s="3" t="s">
         <v>95</v>
@@ -5076,7 +5076,7 @@
         <v>26</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2.6926</v>
+        <v>2.8204</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>15</v>
@@ -5091,7 +5091,7 @@
         <v>0.0888</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.948</v>
+        <v>0.9467</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>14</v>
@@ -5103,13 +5103,13 @@
         <v>0.0783</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.8354</v>
+        <v>0.8343</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.7919</v>
+        <v>0.7898</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>0.2068</v>
+        <v>0.2163</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>95</v>
@@ -5144,7 +5144,7 @@
         <v>26</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2.6926</v>
+        <v>2.8204</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>18</v>
@@ -5159,7 +5159,7 @@
         <v>0.1297</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.8126</v>
+        <v>0.8129</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>28</v>
@@ -5171,13 +5171,13 @@
         <v>0.1543</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>0.9667</v>
+        <v>0.9671</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>0.7856</v>
+        <v>0.7862</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>0.3495</v>
+        <v>0.3662</v>
       </c>
       <c r="T36" s="3" t="s">
         <v>95</v>
@@ -5212,7 +5212,7 @@
         <v>28</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>4.4113</v>
+        <v>4.2835</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>6</v>
@@ -5227,7 +5227,7 @@
         <v>0.1914</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>1.2173</v>
+        <v>1.2177</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>40</v>
@@ -5239,13 +5239,13 @@
         <v>0.2169</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>1.3794</v>
+        <v>1.3799</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>1.6791</v>
+        <v>1.6804</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>1.126</v>
+        <v>1.0938</v>
       </c>
       <c r="T37" s="3" t="s">
         <v>114</v>
@@ -5280,7 +5280,7 @@
         <v>28</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>4.4113</v>
+        <v>4.2835</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>9</v>
@@ -5295,7 +5295,7 @@
         <v>0.0841</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.9303</v>
+        <v>0.9318</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>9</v>
@@ -5307,13 +5307,13 @@
         <v>0.0533</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>0.5893</v>
+        <v>0.5902</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>0.5482</v>
+        <v>0.55</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.2115</v>
+        <v>0.2056</v>
       </c>
       <c r="T38" s="3" t="s">
         <v>103</v>
@@ -5348,7 +5348,7 @@
         <v>28</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>4.4113</v>
+        <v>4.2835</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>12</v>
@@ -5363,7 +5363,7 @@
         <v>0.1053</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>1.0573</v>
+        <v>1.0588</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>13</v>
@@ -5372,16 +5372,16 @@
         <v>180</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>0.0745</v>
+        <v>0.0744</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>0.7475</v>
+        <v>0.7485</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>0.7903</v>
+        <v>0.7925</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>0.3357</v>
+        <v>0.3264</v>
       </c>
       <c r="T39" s="3" t="s">
         <v>95</v>
@@ -5416,7 +5416,7 @@
         <v>28</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>4.4113</v>
+        <v>4.2835</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>0.0926</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.9881</v>
+        <v>0.9867</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>13</v>
@@ -5443,13 +5443,13 @@
         <v>0.074</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>0.7895</v>
+        <v>0.7884</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>0.7801</v>
+        <v>0.778</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.3117</v>
+        <v>0.3023</v>
       </c>
       <c r="T40" s="3" t="s">
         <v>95</v>
@@ -5484,7 +5484,7 @@
         <v>28</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>4.4113</v>
+        <v>4.2835</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>18</v>
@@ -5499,7 +5499,7 @@
         <v>0.1916</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>1.2002</v>
+        <v>1.2006</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>39</v>
@@ -5511,13 +5511,13 @@
         <v>0.212</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>1.3282</v>
+        <v>1.3287</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>1.5941</v>
+        <v>1.5953</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>1.0851</v>
+        <v>1.054</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>114</v>
@@ -5552,7 +5552,7 @@
         <v>26</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>3.4794</v>
+        <v>3.5758</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>6</v>
@@ -5567,7 +5567,7 @@
         <v>0.151</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.9605</v>
+        <v>0.9609</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>30</v>
@@ -5579,13 +5579,13 @@
         <v>0.1837</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>1.1682</v>
+        <v>1.1686</v>
       </c>
       <c r="R42" s="4" t="n">
-        <v>1.122</v>
+        <v>1.1229</v>
       </c>
       <c r="S42" s="4" t="n">
-        <v>0.6104</v>
+        <v>0.6274</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>98</v>
@@ -5620,7 +5620,7 @@
         <v>26</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>3.4794</v>
+        <v>3.5758</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>9</v>
@@ -5635,7 +5635,7 @@
         <v>0.1233</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>1.3634</v>
+        <v>1.3657</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>25</v>
@@ -5647,13 +5647,13 @@
         <v>0.1494</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>1.6519</v>
+        <v>1.6547</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>2.2522</v>
+        <v>2.2599</v>
       </c>
       <c r="S43" s="4" t="n">
-        <v>0.7047</v>
+        <v>0.7252</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>114</v>
@@ -5688,7 +5688,7 @@
         <v>26</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>3.4794</v>
+        <v>3.5758</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>12</v>
@@ -5703,7 +5703,7 @@
         <v>0.0847</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.8501</v>
+        <v>0.8513</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>17</v>
@@ -5712,16 +5712,16 @@
         <v>161</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>0.1051</v>
+        <v>0.105</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>1.0546</v>
+        <v>1.056</v>
       </c>
       <c r="R44" s="4" t="n">
-        <v>0.8965</v>
+        <v>0.8989</v>
       </c>
       <c r="S44" s="4" t="n">
-        <v>0.3089</v>
+        <v>0.3178</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>95</v>
@@ -5756,7 +5756,7 @@
         <v>26</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>3.4794</v>
+        <v>3.5758</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>15</v>
@@ -5771,7 +5771,7 @@
         <v>0.0765</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>0.8161</v>
+        <v>0.8149</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>16</v>
@@ -5783,13 +5783,13 @@
         <v>0.0989</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>1.0551</v>
+        <v>1.0537</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>0.861</v>
+        <v>0.8587</v>
       </c>
       <c r="S45" s="4" t="n">
-        <v>0.2791</v>
+        <v>0.2864</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>95</v>
@@ -5824,7 +5824,7 @@
         <v>26</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>3.4794</v>
+        <v>3.5758</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>18</v>
@@ -5839,7 +5839,7 @@
         <v>0.2061</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>1.2911</v>
+        <v>1.2916</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>21</v>
@@ -5851,13 +5851,13 @@
         <v>0.1331</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>0.8337</v>
+        <v>0.834</v>
       </c>
       <c r="R46" s="4" t="n">
-        <v>1.0764</v>
+        <v>1.0771</v>
       </c>
       <c r="S46" s="4" t="n">
-        <v>0.5944</v>
+        <v>0.6109</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>95</v>
@@ -5892,7 +5892,7 @@
         <v>28</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>3.4782</v>
+        <v>3.3818</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>6</v>
@@ -5907,7 +5907,7 @@
         <v>0.1882</v>
       </c>
       <c r="M47" s="4" t="n">
-        <v>1.1966</v>
+        <v>1.197</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>26</v>
@@ -5919,13 +5919,13 @@
         <v>0.1639</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>1.0422</v>
+        <v>1.0425</v>
       </c>
       <c r="R47" s="4" t="n">
-        <v>1.247</v>
+        <v>1.248</v>
       </c>
       <c r="S47" s="4" t="n">
-        <v>0.6713</v>
+        <v>0.6531</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>98</v>
@@ -5960,7 +5960,7 @@
         <v>28</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>3.4782</v>
+        <v>3.3818</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>9</v>
@@ -5975,7 +5975,7 @@
         <v>0.0497</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.55</v>
+        <v>0.5509</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>13</v>
@@ -5987,13 +5987,13 @@
         <v>0.083</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>0.9179</v>
+        <v>0.9194</v>
       </c>
       <c r="R48" s="4" t="n">
-        <v>0.5049</v>
+        <v>0.5065</v>
       </c>
       <c r="S48" s="4" t="n">
-        <v>0.1563</v>
+        <v>0.1522</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>103</v>
@@ -6028,7 +6028,7 @@
         <v>28</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>3.4782</v>
+        <v>3.3818</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>12</v>
@@ -6043,7 +6043,7 @@
         <v>0.0457</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>0.4586</v>
+        <v>0.4592</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>16</v>
@@ -6055,13 +6055,13 @@
         <v>0.1011</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>1.015</v>
+        <v>1.0164</v>
       </c>
       <c r="R49" s="4" t="n">
-        <v>0.4655</v>
+        <v>0.4667</v>
       </c>
       <c r="S49" s="4" t="n">
-        <v>0.1587</v>
+        <v>0.1546</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>103</v>
@@ -6096,7 +6096,7 @@
         <v>28</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>3.4782</v>
+        <v>3.3818</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>15</v>
@@ -6111,7 +6111,7 @@
         <v>0.0929</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.9909</v>
+        <v>0.9896</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>17</v>
@@ -6123,13 +6123,13 @@
         <v>0.1063</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>1.1346</v>
+        <v>1.1331</v>
       </c>
       <c r="R50" s="4" t="n">
-        <v>1.1243</v>
+        <v>1.1213</v>
       </c>
       <c r="S50" s="4" t="n">
-        <v>0.3607</v>
+        <v>0.3503</v>
       </c>
       <c r="T50" s="3" t="s">
         <v>98</v>
@@ -6164,7 +6164,7 @@
         <v>28</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>3.4782</v>
+        <v>3.3818</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>18</v>
@@ -6179,7 +6179,7 @@
         <v>0.155</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>0.9712</v>
+        <v>0.9715</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>20</v>
@@ -6191,13 +6191,13 @@
         <v>0.1296</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>0.812</v>
+        <v>0.8123</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>0.7886</v>
+        <v>0.7892</v>
       </c>
       <c r="S51" s="4" t="n">
-        <v>0.4309</v>
+        <v>0.4192</v>
       </c>
       <c r="T51" s="3" t="s">
         <v>95</v>
@@ -6232,7 +6232,7 @@
         <v>26</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>3.8452</v>
+        <v>3.8689</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>6</v>
@@ -6247,7 +6247,7 @@
         <v>0.1675</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>1.0649</v>
+        <v>1.0653</v>
       </c>
       <c r="N52" s="4" t="n">
         <v>33</v>
@@ -6259,13 +6259,13 @@
         <v>0.1699</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>1.0806</v>
+        <v>1.081</v>
       </c>
       <c r="R52" s="4" t="n">
-        <v>1.1507</v>
+        <v>1.1516</v>
       </c>
       <c r="S52" s="4" t="n">
-        <v>0.6759</v>
+        <v>0.6804</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>98</v>
@@ -6300,7 +6300,7 @@
         <v>26</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>3.8452</v>
+        <v>3.8689</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>9</v>
@@ -6315,7 +6315,7 @@
         <v>0.0932</v>
       </c>
       <c r="M53" s="4" t="n">
-        <v>1.0309</v>
+        <v>1.0326</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>21</v>
@@ -6327,13 +6327,13 @@
         <v>0.1074</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>1.1874</v>
+        <v>1.1894</v>
       </c>
       <c r="R53" s="4" t="n">
-        <v>1.2241</v>
+        <v>1.2282</v>
       </c>
       <c r="S53" s="4" t="n">
-        <v>0.4136</v>
+        <v>0.4168</v>
       </c>
       <c r="T53" s="3" t="s">
         <v>98</v>
@@ -6368,7 +6368,7 @@
         <v>26</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>3.8452</v>
+        <v>3.8689</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>12</v>
@@ -6383,7 +6383,7 @@
         <v>0.1113</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>1.1171</v>
+        <v>1.1186</v>
       </c>
       <c r="N54" s="4" t="n">
         <v>17</v>
@@ -6395,13 +6395,13 @@
         <v>0.089</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>0.8931</v>
+        <v>0.8943</v>
       </c>
       <c r="R54" s="4" t="n">
-        <v>0.9976</v>
+        <v>1.0004</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>0.3712</v>
+        <v>0.374</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>95</v>
@@ -6436,7 +6436,7 @@
         <v>26</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>3.8452</v>
+        <v>3.8689</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>15</v>
@@ -6451,7 +6451,7 @@
         <v>0.1413</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>1.508</v>
+        <v>1.5058</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>17</v>
@@ -6463,13 +6463,13 @@
         <v>0.0885</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>0.9446</v>
+        <v>0.9433</v>
       </c>
       <c r="R55" s="4" t="n">
-        <v>1.4244</v>
+        <v>1.4205</v>
       </c>
       <c r="S55" s="4" t="n">
-        <v>0.4986</v>
+        <v>0.501</v>
       </c>
       <c r="T55" s="3" t="s">
         <v>114</v>
@@ -6504,7 +6504,7 @@
         <v>26</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>3.8452</v>
+        <v>3.8689</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>18</v>
@@ -6519,7 +6519,7 @@
         <v>0.1328</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.8322</v>
+        <v>0.8325</v>
       </c>
       <c r="N56" s="4" t="n">
         <v>40</v>
@@ -6531,13 +6531,13 @@
         <v>0.2036</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>1.2756</v>
+        <v>1.276</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>1.0616</v>
+        <v>1.0623</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>0.6329</v>
+        <v>0.6371</v>
       </c>
       <c r="T56" s="3" t="s">
         <v>95</v>
@@ -6572,7 +6572,7 @@
         <v>28</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>3.5116</v>
+        <v>3.4878</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>6</v>
@@ -6587,7 +6587,7 @@
         <v>0.133</v>
       </c>
       <c r="M57" s="4" t="n">
-        <v>0.8459</v>
+        <v>0.8462</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>28</v>
@@ -6599,13 +6599,13 @@
         <v>0.1503</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>0.9559</v>
+        <v>0.9563</v>
       </c>
       <c r="R57" s="4" t="n">
-        <v>0.8086</v>
+        <v>0.8092</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>0.4376</v>
+        <v>0.4348</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>95</v>
@@ -6640,7 +6640,7 @@
         <v>28</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>3.5116</v>
+        <v>3.4878</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>9</v>
@@ -6655,7 +6655,7 @@
         <v>0.0653</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.7224</v>
+        <v>0.7236</v>
       </c>
       <c r="N58" s="4" t="n">
         <v>14</v>
@@ -6667,13 +6667,13 @@
         <v>0.0761</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>0.8413</v>
+        <v>0.8426</v>
       </c>
       <c r="R58" s="4" t="n">
-        <v>0.6078</v>
+        <v>0.6098</v>
       </c>
       <c r="S58" s="4" t="n">
-        <v>0.1892</v>
+        <v>0.1882</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>103</v>
@@ -6708,7 +6708,7 @@
         <v>28</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>3.5116</v>
+        <v>3.4878</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>12</v>
@@ -6723,7 +6723,7 @@
         <v>0.1408</v>
       </c>
       <c r="M59" s="4" t="n">
-        <v>1.4134</v>
+        <v>1.4155</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>16</v>
@@ -6735,13 +6735,13 @@
         <v>0.0867</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>0.87</v>
+        <v>0.8712</v>
       </c>
       <c r="R59" s="4" t="n">
-        <v>1.2297</v>
+        <v>1.2332</v>
       </c>
       <c r="S59" s="4" t="n">
-        <v>0.4215</v>
+        <v>0.4193</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>98</v>
@@ -6776,7 +6776,7 @@
         <v>28</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>3.5116</v>
+        <v>3.4878</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>15</v>
@@ -6791,7 +6791,7 @@
         <v>0.0468</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.4996</v>
+        <v>0.4989</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>11</v>
@@ -6803,13 +6803,13 @@
         <v>0.0616</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>0.6571</v>
+        <v>0.6562</v>
       </c>
       <c r="R60" s="4" t="n">
-        <v>0.3283</v>
+        <v>0.3274</v>
       </c>
       <c r="S60" s="4" t="n">
-        <v>0.1059</v>
+        <v>0.105</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>103</v>
@@ -6844,7 +6844,7 @@
         <v>28</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>3.5116</v>
+        <v>3.4878</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>18</v>
@@ -6859,7 +6859,7 @@
         <v>0.1594</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>0.9985</v>
+        <v>0.9988</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>32</v>
@@ -6871,13 +6871,13 @@
         <v>0.1702</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>1.0664</v>
+        <v>1.0667</v>
       </c>
       <c r="R61" s="4" t="n">
-        <v>1.0647</v>
+        <v>1.0655</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>0.5848</v>
+        <v>0.5811</v>
       </c>
       <c r="T61" s="3" t="s">
         <v>95</v>
@@ -6912,7 +6912,7 @@
         <v>26</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>3.845</v>
+        <v>3.7537</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>6</v>
@@ -6927,7 +6927,7 @@
         <v>0.1466</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.9321</v>
+        <v>0.9325</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>32</v>
@@ -6939,13 +6939,13 @@
         <v>0.1598</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>1.0162</v>
+        <v>1.0165</v>
       </c>
       <c r="R62" s="4" t="n">
-        <v>0.9472</v>
+        <v>0.9479</v>
       </c>
       <c r="S62" s="4" t="n">
-        <v>0.5791</v>
+        <v>0.5655</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>95</v>
@@ -6980,7 +6980,7 @@
         <v>26</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>3.845</v>
+        <v>3.7537</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>9</v>
@@ -6995,7 +6995,7 @@
         <v>0.123</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>1.3599</v>
+        <v>1.3623</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>18</v>
@@ -7007,13 +7007,13 @@
         <v>0.09</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>0.9954</v>
+        <v>0.997</v>
       </c>
       <c r="R63" s="4" t="n">
-        <v>1.3537</v>
+        <v>1.3582</v>
       </c>
       <c r="S63" s="4" t="n">
-        <v>0.476</v>
+        <v>0.4654</v>
       </c>
       <c r="T63" s="3" t="s">
         <v>114</v>
@@ -7048,7 +7048,7 @@
         <v>26</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>3.845</v>
+        <v>3.7537</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>12</v>
@@ -7063,7 +7063,7 @@
         <v>0.1097</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>1.1016</v>
+        <v>1.1032</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>19</v>
@@ -7075,13 +7075,13 @@
         <v>0.0953</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>0.9571</v>
+        <v>0.9584</v>
       </c>
       <c r="R64" s="4" t="n">
-        <v>1.0544</v>
+        <v>1.0573</v>
       </c>
       <c r="S64" s="4" t="n">
-        <v>0.4083</v>
+        <v>0.3991</v>
       </c>
       <c r="T64" s="3" t="s">
         <v>95</v>
@@ -7116,7 +7116,7 @@
         <v>26</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>3.845</v>
+        <v>3.7537</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>15</v>
@@ -7131,7 +7131,7 @@
         <v>0.114</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>1.2161</v>
+        <v>1.2144</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>21</v>
@@ -7143,13 +7143,13 @@
         <v>0.1042</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>1.1116</v>
+        <v>1.1101</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>1.3518</v>
+        <v>1.3481</v>
       </c>
       <c r="S65" s="4" t="n">
-        <v>0.4925</v>
+        <v>0.4801</v>
       </c>
       <c r="T65" s="3" t="s">
         <v>114</v>
@@ -7184,7 +7184,7 @@
         <v>26</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>3.845</v>
+        <v>3.7537</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>18</v>
@@ -7199,7 +7199,7 @@
         <v>0.1375</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.8612</v>
+        <v>0.8615</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>27</v>
@@ -7211,13 +7211,13 @@
         <v>0.1368</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>0.8572</v>
+        <v>0.8575</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>0.7382</v>
+        <v>0.7387</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>0.4581</v>
+        <v>0.4473</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>103</v>
@@ -7252,7 +7252,7 @@
         <v>28</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>4.5614</v>
+        <v>4.6527</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>6</v>
@@ -7267,7 +7267,7 @@
         <v>0.1293</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>0.8223</v>
+        <v>0.8226</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>21</v>
@@ -7279,13 +7279,13 @@
         <v>0.1099</v>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>0.6988</v>
+        <v>0.699</v>
       </c>
       <c r="R67" s="4" t="n">
-        <v>0.5746</v>
+        <v>0.575</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>0.4045</v>
+        <v>0.4126</v>
       </c>
       <c r="T67" s="3" t="s">
         <v>103</v>
@@ -7320,7 +7320,7 @@
         <v>28</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>4.5614</v>
+        <v>4.6527</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>9</v>
@@ -7332,10 +7332,10 @@
         <v>220</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.1333</v>
+        <v>0.1332</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>1.4732</v>
+        <v>1.4757</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>21</v>
@@ -7347,13 +7347,13 @@
         <v>0.1049</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>1.1597</v>
+        <v>1.1616</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>1.7084</v>
+        <v>1.7142</v>
       </c>
       <c r="S68" s="4" t="n">
-        <v>0.6918</v>
+        <v>0.7066</v>
       </c>
       <c r="T68" s="3" t="s">
         <v>114</v>
@@ -7388,7 +7388,7 @@
         <v>28</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>4.5614</v>
+        <v>4.6527</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>12</v>
@@ -7403,7 +7403,7 @@
         <v>0.1508</v>
       </c>
       <c r="M69" s="4" t="n">
-        <v>1.514</v>
+        <v>1.5162</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>21</v>
@@ -7415,13 +7415,13 @@
         <v>0.1056</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>1.0599</v>
+        <v>1.0613</v>
       </c>
       <c r="R69" s="4" t="n">
-        <v>1.6047</v>
+        <v>1.6092</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>0.7156</v>
+        <v>0.7307</v>
       </c>
       <c r="T69" s="3" t="s">
         <v>114</v>
@@ -7456,7 +7456,7 @@
         <v>28</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>4.5614</v>
+        <v>4.6527</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>15</v>
@@ -7471,7 +7471,7 @@
         <v>0.0911</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.9722</v>
+        <v>0.9709</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>21</v>
@@ -7483,13 +7483,13 @@
         <v>0.1051</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>1.122</v>
+        <v>1.1205</v>
       </c>
       <c r="R70" s="4" t="n">
-        <v>1.0908</v>
+        <v>1.0878</v>
       </c>
       <c r="S70" s="4" t="n">
-        <v>0.4576</v>
+        <v>0.466</v>
       </c>
       <c r="T70" s="3" t="s">
         <v>95</v>
@@ -7524,7 +7524,7 @@
         <v>28</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>4.5614</v>
+        <v>4.6527</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>18</v>
@@ -7539,7 +7539,7 @@
         <v>0.1379</v>
       </c>
       <c r="M71" s="4" t="n">
-        <v>0.8642</v>
+        <v>0.8645</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>37</v>
@@ -7551,13 +7551,13 @@
         <v>0.1848</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>1.1579</v>
+        <v>1.1583</v>
       </c>
       <c r="R71" s="4" t="n">
-        <v>1.0007</v>
+        <v>1.0014</v>
       </c>
       <c r="S71" s="4" t="n">
-        <v>0.715</v>
+        <v>0.7294</v>
       </c>
       <c r="T71" s="3" t="s">
         <v>95</v>
@@ -7592,7 +7592,7 @@
         <v>26</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>3.8851</v>
+        <v>3.463</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>6</v>
@@ -7607,25 +7607,25 @@
         <v>0.1491</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.9479</v>
+        <v>0.9483</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>0.1393</v>
+        <v>0.1373</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>0.8861</v>
+        <v>0.8733</v>
       </c>
       <c r="R72" s="4" t="n">
-        <v>0.84</v>
+        <v>0.8282</v>
       </c>
       <c r="S72" s="4" t="n">
-        <v>0.5075</v>
+        <v>0.4449</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>95</v>
@@ -7660,7 +7660,7 @@
         <v>26</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>3.8851</v>
+        <v>3.463</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>9</v>
@@ -7675,25 +7675,25 @@
         <v>0.0528</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>0.5833</v>
+        <v>0.5842</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P73" s="4" t="n">
-        <v>0.0751</v>
+        <v>0.0718</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>0.8303</v>
+        <v>0.7956</v>
       </c>
       <c r="R73" s="4" t="n">
-        <v>0.4843</v>
+        <v>0.4648</v>
       </c>
       <c r="S73" s="4" t="n">
-        <v>0.1683</v>
+        <v>0.1434</v>
       </c>
       <c r="T73" s="3" t="s">
         <v>103</v>
@@ -7728,7 +7728,7 @@
         <v>26</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>3.8851</v>
+        <v>3.463</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>12</v>
@@ -7740,28 +7740,28 @@
         <v>182</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.1192</v>
+        <v>0.1191</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>1.1962</v>
+        <v>1.1979</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>29</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>0.1397</v>
+        <v>0.1423</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>1.4024</v>
+        <v>1.4305</v>
       </c>
       <c r="R74" s="4" t="n">
-        <v>1.6775</v>
+        <v>1.7135</v>
       </c>
       <c r="S74" s="4" t="n">
-        <v>0.642</v>
+        <v>0.5825</v>
       </c>
       <c r="T74" s="3" t="s">
         <v>114</v>
@@ -7796,7 +7796,7 @@
         <v>26</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>3.8851</v>
+        <v>3.463</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>15</v>
@@ -7811,25 +7811,25 @@
         <v>0.1136</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>1.2127</v>
+        <v>1.211</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>14</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P75" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.0721</v>
       </c>
       <c r="Q75" s="4" t="n">
-        <v>0.7553</v>
+        <v>0.7683</v>
       </c>
       <c r="R75" s="4" t="n">
-        <v>0.9159</v>
+        <v>0.9304</v>
       </c>
       <c r="S75" s="4" t="n">
-        <v>0.3297</v>
+        <v>0.2984</v>
       </c>
       <c r="T75" s="3" t="s">
         <v>95</v>
@@ -7864,7 +7864,7 @@
         <v>26</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>3.8851</v>
+        <v>3.463</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>18</v>
@@ -7879,25 +7879,25 @@
         <v>0.1543</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.9667</v>
+        <v>0.9671</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>0.1623</v>
+        <v>0.1607</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>1.0171</v>
+        <v>1.0072</v>
       </c>
       <c r="R76" s="4" t="n">
-        <v>0.9832</v>
+        <v>0.974</v>
       </c>
       <c r="S76" s="4" t="n">
-        <v>0.603</v>
+        <v>0.5312</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>95</v>
@@ -7932,7 +7932,7 @@
         <v>28</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>4.4963</v>
+        <v>4.9183</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>6</v>
@@ -7941,13 +7941,13 @@
         <v>21</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>0.12</v>
+        <v>0.1206</v>
       </c>
       <c r="M77" s="4" t="n">
-        <v>0.763</v>
+        <v>0.7671</v>
       </c>
       <c r="N77" s="4" t="n">
         <v>33</v>
@@ -7959,13 +7959,13 @@
         <v>0.1524</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>0.9693</v>
+        <v>0.9697</v>
       </c>
       <c r="R77" s="4" t="n">
-        <v>0.7395</v>
+        <v>0.7439</v>
       </c>
       <c r="S77" s="4" t="n">
-        <v>0.5236</v>
+        <v>0.5753</v>
       </c>
       <c r="T77" s="3" t="s">
         <v>103</v>
@@ -8000,7 +8000,7 @@
         <v>28</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>4.4963</v>
+        <v>4.9183</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>9</v>
@@ -8009,13 +8009,13 @@
         <v>7</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.0431</v>
+        <v>0.0433</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.4765</v>
+        <v>0.4796</v>
       </c>
       <c r="N78" s="4" t="n">
         <v>21</v>
@@ -8027,13 +8027,13 @@
         <v>0.0963</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>1.0651</v>
+        <v>1.0669</v>
       </c>
       <c r="R78" s="4" t="n">
-        <v>0.5075</v>
+        <v>0.5117</v>
       </c>
       <c r="S78" s="4" t="n">
-        <v>0.2067</v>
+        <v>0.2273</v>
       </c>
       <c r="T78" s="3" t="s">
         <v>103</v>
@@ -8068,22 +8068,22 @@
         <v>28</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>4.4963</v>
+        <v>4.9183</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>0.0949</v>
+        <v>0.0902</v>
       </c>
       <c r="M79" s="4" t="n">
-        <v>0.9523</v>
+        <v>0.907</v>
       </c>
       <c r="N79" s="4" t="n">
         <v>16</v>
@@ -8095,13 +8095,13 @@
         <v>0.0755</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R79" s="4" t="n">
-        <v>0.7219</v>
+        <v>0.6884</v>
       </c>
       <c r="S79" s="4" t="n">
-        <v>0.3238</v>
+        <v>0.3369</v>
       </c>
       <c r="T79" s="3" t="s">
         <v>103</v>
@@ -8136,7 +8136,7 @@
         <v>28</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>4.4963</v>
+        <v>4.9183</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>15</v>
@@ -8145,13 +8145,13 @@
         <v>22</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.1199</v>
+        <v>0.1205</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>1.2795</v>
+        <v>1.2843</v>
       </c>
       <c r="N80" s="4" t="n">
         <v>24</v>
@@ -8163,13 +8163,13 @@
         <v>0.1094</v>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>1.1679</v>
+        <v>1.1663</v>
       </c>
       <c r="R80" s="4" t="n">
-        <v>1.4944</v>
+        <v>1.4979</v>
       </c>
       <c r="S80" s="4" t="n">
-        <v>0.6304</v>
+        <v>0.6915</v>
       </c>
       <c r="T80" s="3" t="s">
         <v>114</v>
@@ -8204,7 +8204,7 @@
         <v>28</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>4.4963</v>
+        <v>4.9183</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>18</v>
@@ -8213,13 +8213,13 @@
         <v>45</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>0.2426</v>
+        <v>0.2439</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>1.52</v>
+        <v>1.5283</v>
       </c>
       <c r="N81" s="4" t="n">
         <v>37</v>
@@ -8231,13 +8231,13 @@
         <v>0.1698</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>1.0635</v>
+        <v>1.0639</v>
       </c>
       <c r="R81" s="4" t="n">
-        <v>1.6165</v>
+        <v>1.626</v>
       </c>
       <c r="S81" s="4" t="n">
-        <v>1.1617</v>
+        <v>1.2764</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>114</v>
@@ -8272,7 +8272,7 @@
         <v>28</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>3.9498</v>
+        <v>3.9413</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>6</v>
@@ -8287,7 +8287,7 @@
         <v>0.133</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>0.8455</v>
+        <v>0.8458</v>
       </c>
       <c r="N82" s="4" t="n">
         <v>32</v>
@@ -8299,13 +8299,13 @@
         <v>0.1534</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>0.9755</v>
+        <v>0.9759</v>
       </c>
       <c r="R82" s="4" t="n">
-        <v>0.8248</v>
+        <v>0.8254</v>
       </c>
       <c r="S82" s="4" t="n">
-        <v>0.494</v>
+        <v>0.4932</v>
       </c>
       <c r="T82" s="3" t="s">
         <v>95</v>
@@ -8340,7 +8340,7 @@
         <v>28</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>3.9498</v>
+        <v>3.9413</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>9</v>
@@ -8355,7 +8355,7 @@
         <v>0.0741</v>
       </c>
       <c r="M83" s="4" t="n">
-        <v>0.8191</v>
+        <v>0.8204</v>
       </c>
       <c r="N83" s="4" t="n">
         <v>14</v>
@@ -8364,16 +8364,16 @@
         <v>209</v>
       </c>
       <c r="P83" s="4" t="n">
-        <v>0.0687</v>
+        <v>0.0686</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>0.759</v>
+        <v>0.7602</v>
       </c>
       <c r="R83" s="4" t="n">
-        <v>0.6217</v>
+        <v>0.6237</v>
       </c>
       <c r="S83" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.2141</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>103</v>
@@ -8408,7 +8408,7 @@
         <v>28</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>3.9498</v>
+        <v>3.9413</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>12</v>
@@ -8423,7 +8423,7 @@
         <v>0.1018</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>1.0217</v>
+        <v>1.0231</v>
       </c>
       <c r="N84" s="4" t="n">
         <v>22</v>
@@ -8435,13 +8435,13 @@
         <v>0.1049</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>1.0527</v>
+        <v>1.0541</v>
       </c>
       <c r="R84" s="4" t="n">
-        <v>1.0755</v>
+        <v>1.0785</v>
       </c>
       <c r="S84" s="4" t="n">
-        <v>0.408</v>
+        <v>0.4078</v>
       </c>
       <c r="T84" s="3" t="s">
         <v>95</v>
@@ -8476,7 +8476,7 @@
         <v>28</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>3.9498</v>
+        <v>3.9413</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>15</v>
@@ -8491,7 +8491,7 @@
         <v>0.1149</v>
       </c>
       <c r="M85" s="4" t="n">
-        <v>1.2258</v>
+        <v>1.2241</v>
       </c>
       <c r="N85" s="4" t="n">
         <v>25</v>
@@ -8503,13 +8503,13 @@
         <v>0.1178</v>
       </c>
       <c r="Q85" s="4" t="n">
-        <v>1.2569</v>
+        <v>1.2551</v>
       </c>
       <c r="R85" s="4" t="n">
-        <v>1.5407</v>
+        <v>1.5364</v>
       </c>
       <c r="S85" s="4" t="n">
-        <v>0.5498</v>
+        <v>0.5481</v>
       </c>
       <c r="T85" s="3" t="s">
         <v>114</v>
@@ -8544,7 +8544,7 @@
         <v>28</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>3.9498</v>
+        <v>3.9413</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>18</v>
@@ -8559,7 +8559,7 @@
         <v>0.1196</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>0.7493</v>
+        <v>0.7496</v>
       </c>
       <c r="N86" s="4" t="n">
         <v>19</v>
@@ -8571,13 +8571,13 @@
         <v>0.0958</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>0.6001</v>
+        <v>0.6003</v>
       </c>
       <c r="R86" s="4" t="n">
-        <v>0.4497</v>
+        <v>0.45</v>
       </c>
       <c r="S86" s="4" t="n">
-        <v>0.2734</v>
+        <v>0.273</v>
       </c>
       <c r="T86" s="3" t="s">
         <v>103</v>
@@ -8612,7 +8612,7 @@
         <v>26</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>3.6047</v>
+        <v>3.6131</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>6</v>
@@ -8627,7 +8627,7 @@
         <v>0.157</v>
       </c>
       <c r="M87" s="4" t="n">
-        <v>0.9984</v>
+        <v>0.9987</v>
       </c>
       <c r="N87" s="4" t="n">
         <v>38</v>
@@ -8639,13 +8639,13 @@
         <v>0.1825</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>1.1606</v>
+        <v>1.161</v>
       </c>
       <c r="R87" s="4" t="n">
-        <v>1.1587</v>
+        <v>1.1595</v>
       </c>
       <c r="S87" s="4" t="n">
-        <v>0.6632</v>
+        <v>0.6649</v>
       </c>
       <c r="T87" s="3" t="s">
         <v>98</v>
@@ -8680,7 +8680,7 @@
         <v>26</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>3.6047</v>
+        <v>3.6131</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>9</v>
@@ -8695,7 +8695,7 @@
         <v>0.0928</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>1.026</v>
+        <v>1.0277</v>
       </c>
       <c r="N88" s="4" t="n">
         <v>27</v>
@@ -8707,13 +8707,13 @@
         <v>0.1281</v>
       </c>
       <c r="Q88" s="4" t="n">
-        <v>1.4167</v>
+        <v>1.4191</v>
       </c>
       <c r="R88" s="4" t="n">
-        <v>1.4535</v>
+        <v>1.4584</v>
       </c>
       <c r="S88" s="4" t="n">
-        <v>0.4786</v>
+        <v>0.4804</v>
       </c>
       <c r="T88" s="3" t="s">
         <v>114</v>
@@ -8748,7 +8748,7 @@
         <v>26</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>3.6047</v>
+        <v>3.6131</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>12</v>
@@ -8763,7 +8763,7 @@
         <v>0.0989</v>
       </c>
       <c r="M89" s="4" t="n">
-        <v>0.9928</v>
+        <v>0.9942</v>
       </c>
       <c r="N89" s="4" t="n">
         <v>14</v>
@@ -8775,13 +8775,13 @@
         <v>0.0702</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>0.7051</v>
+        <v>0.7061</v>
       </c>
       <c r="R89" s="4" t="n">
-        <v>0.7001</v>
+        <v>0.702</v>
       </c>
       <c r="S89" s="4" t="n">
-        <v>0.2539</v>
+        <v>0.2547</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>103</v>
@@ -8816,7 +8816,7 @@
         <v>26</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>3.6047</v>
+        <v>3.6131</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>15</v>
@@ -8831,7 +8831,7 @@
         <v>0.0505</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>0.5392</v>
+        <v>0.5386</v>
       </c>
       <c r="N90" s="4" t="n">
         <v>19</v>
@@ -8843,13 +8843,13 @@
         <v>0.0923</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>0.9854</v>
+        <v>0.9841</v>
       </c>
       <c r="R90" s="4" t="n">
-        <v>0.5314</v>
+        <v>0.53</v>
       </c>
       <c r="S90" s="4" t="n">
-        <v>0.1812</v>
+        <v>0.1814</v>
       </c>
       <c r="T90" s="3" t="s">
         <v>103</v>
@@ -8884,7 +8884,7 @@
         <v>26</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>3.6047</v>
+        <v>3.6131</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>18</v>
@@ -8899,7 +8899,7 @@
         <v>0.1944</v>
       </c>
       <c r="M91" s="4" t="n">
-        <v>1.2181</v>
+        <v>1.2185</v>
       </c>
       <c r="N91" s="4" t="n">
         <v>28</v>
@@ -8911,13 +8911,13 @@
         <v>0.1376</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>0.8622</v>
+        <v>0.8625</v>
       </c>
       <c r="R91" s="4" t="n">
-        <v>1.0503</v>
+        <v>1.051</v>
       </c>
       <c r="S91" s="4" t="n">
-        <v>0.6102</v>
+        <v>0.6118</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>95</v>
@@ -8952,22 +8952,22 @@
         <v>26</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>4.7711</v>
+        <v>4.8845</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>0.1544</v>
+        <v>0.1528</v>
       </c>
       <c r="M92" s="4" t="n">
-        <v>0.9816</v>
+        <v>0.9723</v>
       </c>
       <c r="N92" s="4" t="n">
         <v>37</v>
@@ -8979,13 +8979,13 @@
         <v>0.1653</v>
       </c>
       <c r="Q92" s="4" t="n">
-        <v>1.0514</v>
+        <v>1.0518</v>
       </c>
       <c r="R92" s="4" t="n">
-        <v>1.032</v>
+        <v>1.0226</v>
       </c>
       <c r="S92" s="4" t="n">
-        <v>0.7785</v>
+        <v>0.7895</v>
       </c>
       <c r="T92" s="3" t="s">
         <v>95</v>
@@ -9020,22 +9020,22 @@
         <v>26</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>4.7711</v>
+        <v>4.8845</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>0.1385</v>
+        <v>0.1367</v>
       </c>
       <c r="M93" s="4" t="n">
-        <v>1.5308</v>
+        <v>1.5138</v>
       </c>
       <c r="N93" s="4" t="n">
         <v>16</v>
@@ -9047,13 +9047,13 @@
         <v>0.073</v>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>0.8071</v>
+        <v>0.8084</v>
       </c>
       <c r="R93" s="4" t="n">
-        <v>1.2355</v>
+        <v>1.2238</v>
       </c>
       <c r="S93" s="4" t="n">
-        <v>0.5361</v>
+        <v>0.5426</v>
       </c>
       <c r="T93" s="3" t="s">
         <v>98</v>
@@ -9088,7 +9088,7 @@
         <v>26</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>4.7711</v>
+        <v>4.8845</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>12</v>
@@ -9097,13 +9097,13 @@
         <v>17</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>0.0726</v>
+        <v>0.0738</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>0.7291</v>
+        <v>0.7417</v>
       </c>
       <c r="N94" s="4" t="n">
         <v>27</v>
@@ -9115,13 +9115,13 @@
         <v>0.1196</v>
       </c>
       <c r="Q94" s="4" t="n">
-        <v>1.201</v>
+        <v>1.2027</v>
       </c>
       <c r="R94" s="4" t="n">
-        <v>0.8757</v>
+        <v>0.8921</v>
       </c>
       <c r="S94" s="4" t="n">
-        <v>0.4184</v>
+        <v>0.4358</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>95</v>
@@ -9156,7 +9156,7 @@
         <v>26</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>4.7711</v>
+        <v>4.8845</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>15</v>
@@ -9165,13 +9165,13 @@
         <v>14</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>0.0605</v>
+        <v>0.0615</v>
       </c>
       <c r="M95" s="4" t="n">
-        <v>0.6461</v>
+        <v>0.6555</v>
       </c>
       <c r="N95" s="4" t="n">
         <v>23</v>
@@ -9183,13 +9183,13 @@
         <v>0.1025</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>1.094</v>
+        <v>1.0924</v>
       </c>
       <c r="R95" s="4" t="n">
-        <v>0.7068</v>
+        <v>0.7161</v>
       </c>
       <c r="S95" s="4" t="n">
-        <v>0.3177</v>
+        <v>0.33</v>
       </c>
       <c r="T95" s="3" t="s">
         <v>103</v>
@@ -9224,22 +9224,22 @@
         <v>26</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>4.7711</v>
+        <v>4.8845</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.135</v>
+        <v>0.1331</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>0.8456</v>
+        <v>0.8345</v>
       </c>
       <c r="N96" s="4" t="n">
         <v>37</v>
@@ -9251,13 +9251,13 @@
         <v>0.1655</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>1.0368</v>
+        <v>1.0372</v>
       </c>
       <c r="R96" s="4" t="n">
-        <v>0.8767</v>
+        <v>0.8655</v>
       </c>
       <c r="S96" s="4" t="n">
-        <v>0.6713</v>
+        <v>0.6782</v>
       </c>
       <c r="T96" s="3" t="s">
         <v>95</v>
@@ -9292,7 +9292,7 @@
         <v>28</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>2.8091</v>
+        <v>2.6956</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>6</v>
@@ -9307,25 +9307,25 @@
         <v>0.1887</v>
       </c>
       <c r="M97" s="4" t="n">
-        <v>1.2001</v>
+        <v>1.2005</v>
       </c>
       <c r="N97" s="4" t="n">
         <v>30</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P97" s="4" t="n">
-        <v>0.1602</v>
+        <v>0.161</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>1.0186</v>
+        <v>1.024</v>
       </c>
       <c r="R97" s="4" t="n">
-        <v>1.2224</v>
+        <v>1.2293</v>
       </c>
       <c r="S97" s="4" t="n">
-        <v>0.5514</v>
+        <v>0.5322</v>
       </c>
       <c r="T97" s="3" t="s">
         <v>98</v>
@@ -9360,7 +9360,7 @@
         <v>28</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>2.8091</v>
+        <v>2.6956</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>9</v>
@@ -9372,28 +9372,28 @@
         <v>151</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>0.1165</v>
+        <v>0.1164</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>1.2874</v>
+        <v>1.2896</v>
       </c>
       <c r="N98" s="4" t="n">
         <v>14</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P98" s="4" t="n">
-        <v>0.0761</v>
+        <v>0.0765</v>
       </c>
       <c r="Q98" s="4" t="n">
-        <v>0.8413</v>
+        <v>0.8468</v>
       </c>
       <c r="R98" s="4" t="n">
-        <v>1.0831</v>
+        <v>1.092</v>
       </c>
       <c r="S98" s="4" t="n">
-        <v>0.281</v>
+        <v>0.2716</v>
       </c>
       <c r="T98" s="3" t="s">
         <v>95</v>
@@ -9428,7 +9428,7 @@
         <v>28</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>2.8091</v>
+        <v>2.6956</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>12</v>
@@ -9443,25 +9443,25 @@
         <v>0.1113</v>
       </c>
       <c r="M99" s="4" t="n">
-        <v>1.1177</v>
+        <v>1.1192</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P99" s="4" t="n">
-        <v>0.0867</v>
+        <v>0.0821</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>0.87</v>
+        <v>0.8258</v>
       </c>
       <c r="R99" s="4" t="n">
-        <v>0.9724</v>
+        <v>0.9242</v>
       </c>
       <c r="S99" s="4" t="n">
-        <v>0.2779</v>
+        <v>0.2532</v>
       </c>
       <c r="T99" s="3" t="s">
         <v>95</v>
@@ -9496,7 +9496,7 @@
         <v>28</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>2.8091</v>
+        <v>2.6956</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>15</v>
@@ -9511,28 +9511,28 @@
         <v>0.0569</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>0.607</v>
+        <v>0.6063</v>
       </c>
       <c r="N100" s="4" t="n">
         <v>22</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P100" s="4" t="n">
-        <v>0.1158</v>
+        <v>0.1163</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>1.2354</v>
+        <v>1.2398</v>
       </c>
       <c r="R100" s="4" t="n">
-        <v>0.7499</v>
+        <v>0.7517</v>
       </c>
       <c r="S100" s="4" t="n">
-        <v>0.2016</v>
+        <v>0.1943</v>
       </c>
       <c r="T100" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>274</v>
@@ -9564,7 +9564,7 @@
         <v>28</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>2.8091</v>
+        <v>2.6956</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>18</v>
@@ -9579,25 +9579,25 @@
         <v>0.171</v>
       </c>
       <c r="M101" s="4" t="n">
-        <v>1.0712</v>
+        <v>1.0715</v>
       </c>
       <c r="N101" s="4" t="n">
         <v>35</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P101" s="4" t="n">
-        <v>0.185</v>
+        <v>0.1859</v>
       </c>
       <c r="Q101" s="4" t="n">
-        <v>1.159</v>
+        <v>1.1651</v>
       </c>
       <c r="R101" s="4" t="n">
-        <v>1.2414</v>
+        <v>1.2484</v>
       </c>
       <c r="S101" s="4" t="n">
-        <v>0.5684</v>
+        <v>0.5487</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>98</v>
@@ -9681,7 +9681,7 @@
         <v>0.1466</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.9321</v>
+        <v>0.9325</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>21</v>
@@ -9693,7 +9693,7 @@
         <v>0.1099</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.6988</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="3">
@@ -9713,7 +9713,7 @@
         <v>0.123</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1.3599</v>
+        <v>1.3623</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>21</v>
@@ -9725,7 +9725,7 @@
         <v>0.1049</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1.1597</v>
+        <v>1.1616</v>
       </c>
     </row>
     <row r="4">
@@ -9745,7 +9745,7 @@
         <v>0.1097</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.1016</v>
+        <v>1.1032</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>21</v>
@@ -9757,7 +9757,7 @@
         <v>0.1056</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1.0599</v>
+        <v>1.0613</v>
       </c>
     </row>
     <row r="5">
@@ -9777,7 +9777,7 @@
         <v>0.114</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.2161</v>
+        <v>1.2144</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>21</v>
@@ -9789,7 +9789,7 @@
         <v>0.1051</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1.122</v>
+        <v>1.1205</v>
       </c>
     </row>
     <row r="6">
@@ -9809,7 +9809,7 @@
         <v>0.1375</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.8612</v>
+        <v>0.8615</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>0.1848</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.1579</v>
+        <v>1.1583</v>
       </c>
     </row>
     <row r="7">
@@ -9841,7 +9841,7 @@
         <v>0.133</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.8455</v>
+        <v>0.8458</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>38</v>
@@ -9853,7 +9853,7 @@
         <v>0.1825</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.1606</v>
+        <v>1.161</v>
       </c>
     </row>
     <row r="8">
@@ -9873,7 +9873,7 @@
         <v>0.0741</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.8191</v>
+        <v>0.8204</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>27</v>
@@ -9885,7 +9885,7 @@
         <v>0.1281</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.4167</v>
+        <v>1.4191</v>
       </c>
     </row>
     <row r="9">
@@ -9905,7 +9905,7 @@
         <v>0.1018</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.0217</v>
+        <v>1.0231</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>14</v>
@@ -9917,7 +9917,7 @@
         <v>0.0702</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.7051</v>
+        <v>0.7061</v>
       </c>
     </row>
     <row r="10">
@@ -9937,7 +9937,7 @@
         <v>0.1149</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.2258</v>
+        <v>1.2241</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>19</v>
@@ -9949,7 +9949,7 @@
         <v>0.0923</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.9854</v>
+        <v>0.9841</v>
       </c>
     </row>
     <row r="11">
@@ -9969,7 +9969,7 @@
         <v>0.1196</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.7493</v>
+        <v>0.7496</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>28</v>
@@ -9981,7 +9981,7 @@
         <v>0.1376</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.8622</v>
+        <v>0.8625</v>
       </c>
     </row>
     <row r="12">
@@ -10001,7 +10001,7 @@
         <v>0.1549</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.985</v>
+        <v>0.9854</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>40</v>
@@ -10013,7 +10013,7 @@
         <v>0.2169</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.3794</v>
+        <v>1.3799</v>
       </c>
     </row>
     <row r="13">
@@ -10033,7 +10033,7 @@
         <v>0.0784</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.8669</v>
+        <v>0.8683</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>9</v>
@@ -10045,7 +10045,7 @@
         <v>0.0533</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5893</v>
+        <v>0.5902</v>
       </c>
     </row>
     <row r="14">
@@ -10065,7 +10065,7 @@
         <v>0.0639</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6417</v>
+        <v>0.6426</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>13</v>
@@ -10074,10 +10074,10 @@
         <v>180</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.0745</v>
+        <v>0.0744</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7475</v>
+        <v>0.7485</v>
       </c>
     </row>
     <row r="15">
@@ -10097,7 +10097,7 @@
         <v>0.0888</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.948</v>
+        <v>0.9467</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>13</v>
@@ -10109,7 +10109,7 @@
         <v>0.074</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.7895</v>
+        <v>0.7884</v>
       </c>
     </row>
     <row r="16">
@@ -10129,7 +10129,7 @@
         <v>0.1297</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8126</v>
+        <v>0.8129</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>39</v>
@@ -10141,7 +10141,7 @@
         <v>0.212</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.3282</v>
+        <v>1.3287</v>
       </c>
     </row>
     <row r="17">
@@ -10152,28 +10152,28 @@
         <v>6</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1544</v>
+        <v>0.1528</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.9816</v>
+        <v>0.9723</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1602</v>
+        <v>0.161</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.0186</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="18">
@@ -10184,28 +10184,28 @@
         <v>9</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1385</v>
+        <v>0.1367</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.5308</v>
+        <v>1.5138</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.0761</v>
+        <v>0.0765</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8413</v>
+        <v>0.8468</v>
       </c>
     </row>
     <row r="19">
@@ -10219,25 +10219,25 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.0726</v>
+        <v>0.0738</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7291</v>
+        <v>0.7417</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.0867</v>
+        <v>0.0821</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.87</v>
+        <v>0.8258</v>
       </c>
     </row>
     <row r="20">
@@ -10251,25 +10251,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.0605</v>
+        <v>0.0615</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6461</v>
+        <v>0.6555</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>22</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1158</v>
+        <v>0.1163</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.2354</v>
+        <v>1.2398</v>
       </c>
     </row>
     <row r="21">
@@ -10280,28 +10280,28 @@
         <v>18</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.135</v>
+        <v>0.1331</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.8456</v>
+        <v>0.8345</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>35</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.185</v>
+        <v>0.1859</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.159</v>
+        <v>1.1651</v>
       </c>
     </row>
     <row r="22">
@@ -10321,7 +10321,7 @@
         <v>0.1293</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.8223</v>
+        <v>0.8226</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>32</v>
@@ -10333,7 +10333,7 @@
         <v>0.1598</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.0162</v>
+        <v>1.0165</v>
       </c>
     </row>
     <row r="23">
@@ -10350,10 +10350,10 @@
         <v>220</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1333</v>
+        <v>0.1332</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.4732</v>
+        <v>1.4757</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>18</v>
@@ -10365,7 +10365,7 @@
         <v>0.09</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.9954</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="24">
@@ -10385,7 +10385,7 @@
         <v>0.1508</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.514</v>
+        <v>1.5162</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>19</v>
@@ -10397,7 +10397,7 @@
         <v>0.0953</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.9571</v>
+        <v>0.9584</v>
       </c>
     </row>
     <row r="25">
@@ -10417,7 +10417,7 @@
         <v>0.0911</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.9722</v>
+        <v>0.9709</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>21</v>
@@ -10429,7 +10429,7 @@
         <v>0.1042</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.1116</v>
+        <v>1.1101</v>
       </c>
     </row>
     <row r="26">
@@ -10449,7 +10449,7 @@
         <v>0.1379</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.8642</v>
+        <v>0.8645</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>27</v>
@@ -10461,7 +10461,7 @@
         <v>0.1368</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.8572</v>
+        <v>0.8575</v>
       </c>
     </row>
     <row r="27">
@@ -10481,7 +10481,7 @@
         <v>0.1872</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.1907</v>
+        <v>1.1911</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>36</v>
@@ -10490,10 +10490,10 @@
         <v>235</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.1535</v>
+        <v>0.1534</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.9758</v>
+        <v>0.9762</v>
       </c>
     </row>
     <row r="28">
@@ -10513,7 +10513,7 @@
         <v>0.0863</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.9541</v>
+        <v>0.9556</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>20</v>
@@ -10525,7 +10525,7 @@
         <v>0.0854</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.9447</v>
+        <v>0.9462</v>
       </c>
     </row>
     <row r="29">
@@ -10545,7 +10545,7 @@
         <v>0.0648</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.6502</v>
+        <v>0.651</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>25</v>
@@ -10554,10 +10554,10 @@
         <v>235</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.106</v>
+        <v>0.1059</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.0636</v>
+        <v>1.0651</v>
       </c>
     </row>
     <row r="30">
@@ -10577,7 +10577,7 @@
         <v>0.0922</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.9837</v>
+        <v>0.9824</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>23</v>
@@ -10589,7 +10589,7 @@
         <v>0.0976</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.0417</v>
+        <v>1.0402</v>
       </c>
     </row>
     <row r="31">
@@ -10609,7 +10609,7 @@
         <v>0.1539</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.9644</v>
+        <v>0.9647</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>38</v>
@@ -10621,7 +10621,7 @@
         <v>0.1616</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.0122</v>
+        <v>1.0126</v>
       </c>
     </row>
     <row r="32">
@@ -10641,7 +10641,7 @@
         <v>0.1675</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.0649</v>
+        <v>1.0653</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>0.1503</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.9559</v>
+        <v>0.9563</v>
       </c>
     </row>
     <row r="33">
@@ -10673,7 +10673,7 @@
         <v>0.0932</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.0309</v>
+        <v>1.0326</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>14</v>
@@ -10685,7 +10685,7 @@
         <v>0.0761</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.8413</v>
+        <v>0.8426</v>
       </c>
     </row>
     <row r="34">
@@ -10705,7 +10705,7 @@
         <v>0.1113</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.1171</v>
+        <v>1.1186</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>16</v>
@@ -10717,7 +10717,7 @@
         <v>0.0867</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.87</v>
+        <v>0.8712</v>
       </c>
     </row>
     <row r="35">
@@ -10737,7 +10737,7 @@
         <v>0.1413</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.508</v>
+        <v>1.5058</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>11</v>
@@ -10749,7 +10749,7 @@
         <v>0.0616</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.6571</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="36">
@@ -10769,7 +10769,7 @@
         <v>0.1328</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.8322</v>
+        <v>0.8325</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>32</v>
@@ -10781,7 +10781,7 @@
         <v>0.1702</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.0664</v>
+        <v>1.0667</v>
       </c>
     </row>
     <row r="37">
@@ -10801,7 +10801,7 @@
         <v>0.133</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.8459</v>
+        <v>0.8462</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>33</v>
@@ -10813,7 +10813,7 @@
         <v>0.1699</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.0806</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="38">
@@ -10833,7 +10833,7 @@
         <v>0.0653</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.7224</v>
+        <v>0.7236</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>21</v>
@@ -10845,7 +10845,7 @@
         <v>0.1074</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.1874</v>
+        <v>1.1894</v>
       </c>
     </row>
     <row r="39">
@@ -10865,7 +10865,7 @@
         <v>0.1408</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1.4134</v>
+        <v>1.4155</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>17</v>
@@ -10877,7 +10877,7 @@
         <v>0.089</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.8931</v>
+        <v>0.8943</v>
       </c>
     </row>
     <row r="40">
@@ -10897,7 +10897,7 @@
         <v>0.0468</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.4996</v>
+        <v>0.4989</v>
       </c>
       <c r="G40" s="4" t="n">
         <v>17</v>
@@ -10909,7 +10909,7 @@
         <v>0.0885</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.9446</v>
+        <v>0.9433</v>
       </c>
     </row>
     <row r="41">
@@ -10929,7 +10929,7 @@
         <v>0.1594</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.9985</v>
+        <v>0.9988</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>40</v>
@@ -10941,7 +10941,7 @@
         <v>0.2036</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.2756</v>
+        <v>1.276</v>
       </c>
     </row>
     <row r="42">
@@ -10961,7 +10961,7 @@
         <v>0.157</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.9984</v>
+        <v>0.9987</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>32</v>
@@ -10973,7 +10973,7 @@
         <v>0.1534</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.9755</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="43">
@@ -10993,7 +10993,7 @@
         <v>0.0928</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1.026</v>
+        <v>1.0277</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>14</v>
@@ -11002,10 +11002,10 @@
         <v>209</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0.0687</v>
+        <v>0.0686</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0.759</v>
+        <v>0.7602</v>
       </c>
     </row>
     <row r="44">
@@ -11025,7 +11025,7 @@
         <v>0.0989</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.9928</v>
+        <v>0.9942</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>22</v>
@@ -11037,7 +11037,7 @@
         <v>0.1049</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.0527</v>
+        <v>1.0541</v>
       </c>
     </row>
     <row r="45">
@@ -11057,7 +11057,7 @@
         <v>0.0505</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.5392</v>
+        <v>0.5386</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>25</v>
@@ -11069,7 +11069,7 @@
         <v>0.1178</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.2569</v>
+        <v>1.2551</v>
       </c>
     </row>
     <row r="46">
@@ -11089,7 +11089,7 @@
         <v>0.1944</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1.2181</v>
+        <v>1.2185</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>19</v>
@@ -11101,7 +11101,7 @@
         <v>0.0958</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0.6001</v>
+        <v>0.6003</v>
       </c>
     </row>
     <row r="47">
@@ -11121,7 +11121,7 @@
         <v>0.1721</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1.0943</v>
+        <v>1.0947</v>
       </c>
       <c r="G47" s="4" t="n">
         <v>41</v>
@@ -11133,7 +11133,7 @@
         <v>0.1836</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.1676</v>
+        <v>1.168</v>
       </c>
     </row>
     <row r="48">
@@ -11153,7 +11153,7 @@
         <v>0.0663</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.7327</v>
+        <v>0.7339</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>20</v>
@@ -11165,7 +11165,7 @@
         <v>0.0905</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1.0005</v>
+        <v>1.0021</v>
       </c>
     </row>
     <row r="49">
@@ -11185,7 +11185,7 @@
         <v>0.1036</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.0404</v>
+        <v>1.0419</v>
       </c>
       <c r="G49" s="4" t="n">
         <v>17</v>
@@ -11194,10 +11194,10 @@
         <v>221</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>0.0785</v>
+        <v>0.0784</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>0.7876</v>
+        <v>0.7887</v>
       </c>
     </row>
     <row r="50">
@@ -11217,7 +11217,7 @@
         <v>0.1307</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1.3951</v>
+        <v>1.3932</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>19</v>
@@ -11229,7 +11229,7 @@
         <v>0.0865</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>0.9231</v>
+        <v>0.9218</v>
       </c>
     </row>
     <row r="51">
@@ -11249,7 +11249,7 @@
         <v>0.1723</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1.0792</v>
+        <v>1.0796</v>
       </c>
       <c r="G51" s="4" t="n">
         <v>31</v>
@@ -11261,7 +11261,7 @@
         <v>0.1416</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>0.887</v>
+        <v>0.8873</v>
       </c>
     </row>
     <row r="52">
@@ -11281,7 +11281,7 @@
         <v>0.1491</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.9479</v>
+        <v>0.9483</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>33</v>
@@ -11293,7 +11293,7 @@
         <v>0.1524</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>0.9693</v>
+        <v>0.9697</v>
       </c>
     </row>
     <row r="53">
@@ -11313,7 +11313,7 @@
         <v>0.0528</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.5833</v>
+        <v>0.5842</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>21</v>
@@ -11325,7 +11325,7 @@
         <v>0.0963</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.0651</v>
+        <v>1.0669</v>
       </c>
     </row>
     <row r="54">
@@ -11342,10 +11342,10 @@
         <v>182</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.1192</v>
+        <v>0.1191</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1.1962</v>
+        <v>1.1979</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>16</v>
@@ -11357,7 +11357,7 @@
         <v>0.0755</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="55">
@@ -11377,7 +11377,7 @@
         <v>0.1136</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.2127</v>
+        <v>1.211</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>24</v>
@@ -11389,7 +11389,7 @@
         <v>0.1094</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1.1679</v>
+        <v>1.1663</v>
       </c>
     </row>
     <row r="56">
@@ -11409,7 +11409,7 @@
         <v>0.1543</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.9667</v>
+        <v>0.9671</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>37</v>
@@ -11421,7 +11421,7 @@
         <v>0.1698</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>1.0635</v>
+        <v>1.0639</v>
       </c>
     </row>
     <row r="57">
@@ -11441,7 +11441,7 @@
         <v>0.151</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.9605</v>
+        <v>0.9609</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>26</v>
@@ -11453,7 +11453,7 @@
         <v>0.1639</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>1.0422</v>
+        <v>1.0425</v>
       </c>
     </row>
     <row r="58">
@@ -11473,7 +11473,7 @@
         <v>0.1233</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1.3634</v>
+        <v>1.3657</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>13</v>
@@ -11485,7 +11485,7 @@
         <v>0.083</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>0.9179</v>
+        <v>0.9194</v>
       </c>
     </row>
     <row r="59">
@@ -11505,7 +11505,7 @@
         <v>0.0847</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.8501</v>
+        <v>0.8513</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>16</v>
@@ -11517,7 +11517,7 @@
         <v>0.1011</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>1.015</v>
+        <v>1.0164</v>
       </c>
     </row>
     <row r="60">
@@ -11537,7 +11537,7 @@
         <v>0.0765</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.8161</v>
+        <v>0.8149</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>17</v>
@@ -11549,7 +11549,7 @@
         <v>0.1063</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>1.1346</v>
+        <v>1.1331</v>
       </c>
     </row>
     <row r="61">
@@ -11569,7 +11569,7 @@
         <v>0.2061</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1.2911</v>
+        <v>1.2916</v>
       </c>
       <c r="G61" s="4" t="n">
         <v>20</v>
@@ -11581,7 +11581,7 @@
         <v>0.1296</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>0.812</v>
+        <v>0.8123</v>
       </c>
     </row>
     <row r="62">
@@ -11595,25 +11595,25 @@
         <v>21</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.12</v>
+        <v>0.1206</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.763</v>
+        <v>0.7671</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>0.1393</v>
+        <v>0.1373</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>0.8861</v>
+        <v>0.8733</v>
       </c>
     </row>
     <row r="63">
@@ -11627,25 +11627,25 @@
         <v>7</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.0431</v>
+        <v>0.0433</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.4765</v>
+        <v>0.4796</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>0.0751</v>
+        <v>0.0718</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>0.8303</v>
+        <v>0.7956</v>
       </c>
     </row>
     <row r="64">
@@ -11656,28 +11656,28 @@
         <v>12</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.0949</v>
+        <v>0.0902</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.9523</v>
+        <v>0.907</v>
       </c>
       <c r="G64" s="4" t="n">
         <v>29</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>0.1397</v>
+        <v>0.1423</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>1.4024</v>
+        <v>1.4305</v>
       </c>
     </row>
     <row r="65">
@@ -11691,25 +11691,25 @@
         <v>22</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.1199</v>
+        <v>0.1205</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1.2795</v>
+        <v>1.2843</v>
       </c>
       <c r="G65" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.0721</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>0.7553</v>
+        <v>0.7683</v>
       </c>
     </row>
     <row r="66">
@@ -11723,25 +11723,25 @@
         <v>45</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.2426</v>
+        <v>0.2439</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1.52</v>
+        <v>1.5283</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>0.1623</v>
+        <v>0.1607</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>1.0171</v>
+        <v>1.0072</v>
       </c>
     </row>
     <row r="67">
@@ -11761,7 +11761,7 @@
         <v>0.1887</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1.2001</v>
+        <v>1.2005</v>
       </c>
       <c r="G67" s="4" t="n">
         <v>37</v>
@@ -11773,7 +11773,7 @@
         <v>0.1653</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>1.0514</v>
+        <v>1.0518</v>
       </c>
     </row>
     <row r="68">
@@ -11790,10 +11790,10 @@
         <v>151</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.1165</v>
+        <v>0.1164</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1.2874</v>
+        <v>1.2896</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>16</v>
@@ -11805,7 +11805,7 @@
         <v>0.073</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>0.8071</v>
+        <v>0.8084</v>
       </c>
     </row>
     <row r="69">
@@ -11825,7 +11825,7 @@
         <v>0.1113</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1.1177</v>
+        <v>1.1192</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>27</v>
@@ -11837,7 +11837,7 @@
         <v>0.1196</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>1.201</v>
+        <v>1.2027</v>
       </c>
     </row>
     <row r="70">
@@ -11857,7 +11857,7 @@
         <v>0.0569</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0.607</v>
+        <v>0.6063</v>
       </c>
       <c r="G70" s="4" t="n">
         <v>23</v>
@@ -11869,7 +11869,7 @@
         <v>0.1025</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>1.094</v>
+        <v>1.0924</v>
       </c>
     </row>
     <row r="71">
@@ -11889,7 +11889,7 @@
         <v>0.171</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1.0712</v>
+        <v>1.0715</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>0.1655</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>1.0368</v>
+        <v>1.0372</v>
       </c>
     </row>
     <row r="72">
@@ -11921,7 +11921,7 @@
         <v>0.1914</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1.2173</v>
+        <v>1.2177</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>22</v>
@@ -11933,7 +11933,7 @@
         <v>0.1238</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0.7874</v>
+        <v>0.7877</v>
       </c>
     </row>
     <row r="73">
@@ -11953,7 +11953,7 @@
         <v>0.0841</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>0.9303</v>
+        <v>0.9318</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>17</v>
@@ -11965,7 +11965,7 @@
         <v>0.0932</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1.03</v>
+        <v>1.0317</v>
       </c>
     </row>
     <row r="74">
@@ -11985,7 +11985,7 @@
         <v>0.1053</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1.0573</v>
+        <v>1.0588</v>
       </c>
       <c r="G74" s="4" t="n">
         <v>25</v>
@@ -11997,7 +11997,7 @@
         <v>0.1343</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>1.3483</v>
+        <v>1.3502</v>
       </c>
     </row>
     <row r="75">
@@ -12017,7 +12017,7 @@
         <v>0.0926</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>0.9881</v>
+        <v>0.9867</v>
       </c>
       <c r="G75" s="4" t="n">
         <v>14</v>
@@ -12029,7 +12029,7 @@
         <v>0.0783</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>0.8354</v>
+        <v>0.8343</v>
       </c>
     </row>
     <row r="76">
@@ -12049,7 +12049,7 @@
         <v>0.1916</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1.2002</v>
+        <v>1.2006</v>
       </c>
       <c r="G76" s="4" t="n">
         <v>28</v>
@@ -12061,7 +12061,7 @@
         <v>0.1543</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>0.9667</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="77">
@@ -12081,7 +12081,7 @@
         <v>0.1882</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1.1966</v>
+        <v>1.197</v>
       </c>
       <c r="G77" s="4" t="n">
         <v>30</v>
@@ -12093,7 +12093,7 @@
         <v>0.1837</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>1.1682</v>
+        <v>1.1686</v>
       </c>
     </row>
     <row r="78">
@@ -12113,7 +12113,7 @@
         <v>0.0497</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0.55</v>
+        <v>0.5509</v>
       </c>
       <c r="G78" s="4" t="n">
         <v>25</v>
@@ -12125,7 +12125,7 @@
         <v>0.1494</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>1.6519</v>
+        <v>1.6547</v>
       </c>
     </row>
     <row r="79">
@@ -12145,7 +12145,7 @@
         <v>0.0457</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0.4586</v>
+        <v>0.4592</v>
       </c>
       <c r="G79" s="4" t="n">
         <v>17</v>
@@ -12154,10 +12154,10 @@
         <v>161</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>0.1051</v>
+        <v>0.105</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>1.0546</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="80">
@@ -12177,7 +12177,7 @@
         <v>0.0929</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0.9909</v>
+        <v>0.9896</v>
       </c>
       <c r="G80" s="4" t="n">
         <v>16</v>
@@ -12189,7 +12189,7 @@
         <v>0.0989</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>1.0551</v>
+        <v>1.0537</v>
       </c>
     </row>
     <row r="81">
@@ -12209,7 +12209,7 @@
         <v>0.155</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0.9712</v>
+        <v>0.9715</v>
       </c>
       <c r="G81" s="4" t="n">
         <v>21</v>
@@ -12221,7 +12221,7 @@
         <v>0.1331</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>0.8337</v>
+        <v>0.834</v>
       </c>
     </row>
     <row r="82">
@@ -12241,7 +12241,7 @@
         <v>0.1658</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1.0545</v>
+        <v>1.0548</v>
       </c>
       <c r="G82" s="4" t="n">
         <v>25</v>
@@ -12253,7 +12253,7 @@
         <v>0.1151</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>0.7321</v>
+        <v>0.7324</v>
       </c>
     </row>
     <row r="83">
@@ -12273,7 +12273,7 @@
         <v>0.1036</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1.1458</v>
+        <v>1.1477</v>
       </c>
       <c r="G83" s="4" t="n">
         <v>21</v>
@@ -12285,7 +12285,7 @@
         <v>0.0939</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>1.0384</v>
+        <v>1.0401</v>
       </c>
     </row>
     <row r="84">
@@ -12305,7 +12305,7 @@
         <v>0.0988</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0.9922</v>
+        <v>0.9936</v>
       </c>
       <c r="G84" s="4" t="n">
         <v>27</v>
@@ -12317,7 +12317,7 @@
         <v>0.1196</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>1.201</v>
+        <v>1.2027</v>
       </c>
     </row>
     <row r="85">
@@ -12337,7 +12337,7 @@
         <v>0.1208</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1.289</v>
+        <v>1.2872</v>
       </c>
       <c r="G85" s="4" t="n">
         <v>18</v>
@@ -12349,7 +12349,7 @@
         <v>0.0816</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>0.8707</v>
+        <v>0.8695</v>
       </c>
     </row>
     <row r="86">
@@ -12369,7 +12369,7 @@
         <v>0.1211</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>0.7586</v>
+        <v>0.7589</v>
       </c>
       <c r="G86" s="4" t="n">
         <v>38</v>
@@ -12381,7 +12381,7 @@
         <v>0.1697</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>1.063</v>
+        <v>1.0634</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_try_channel_matchups.xlsx
+++ b/files/NRL_try_channel_matchups.xlsx
@@ -98,13 +98,13 @@
     <t xml:space="preserve">away</t>
   </si>
   <si>
-    <t xml:space="preserve">fullback 1.34 (off 0.98 x def 1.37): Kalyn Ponga</t>
+    <t xml:space="preserve">fullback 1.29 (off 0.97 x def 1.33): Kalyn Ponga</t>
   </si>
   <si>
     <t xml:space="preserve">home</t>
   </si>
   <si>
-    <t xml:space="preserve">right_centre 1.92 (off 1.42 x def 1.35): Tallis Duncan</t>
+    <t xml:space="preserve">right_centre 1.94 (off 1.42 x def 1.36): Latrell Mitchell</t>
   </si>
   <si>
     <t xml:space="preserve">18:05</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">left_centre 1.86 (off 1.36 x def 1.37): Herbie Farnworth; fullback 1.65 (off 1.52 x def 1.09): Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_wing 1.13 (off 1.11 x def 1.02): Alofiana Khan-Pereira</t>
+    <t xml:space="preserve">left_centre 1.97 (off 1.37 x def 1.44): Herbie Farnworth; fullback 1.63 (off 1.56 x def 1.05): Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No wing/centre/fullback focus &gt;= 1.12</t>
   </si>
   <si>
     <t xml:space="preserve">cronulla-sutherland sharks v north queensland cowboys</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">cronulla-sutherland sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">right_centre 1.54 (off 1.26 x def 1.23): Jaxon Purdue; right_wing 1.14 (off 1.00 x def 1.14): Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_wing 1.17 (off 0.92 x def 1.27): Ronaldo Mulitalo; left_centre 1.38 (off 1.43 x def 0.96): KL Iro</t>
+    <t xml:space="preserve">right_centre 1.51 (off 1.24 x def 1.21): Jaxon Purdue; right_wing 1.15 (off 1.02 x def 1.13): Braidon Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left_wing 1.17 (off 0.90 x def 1.30): Ronaldo Mulitalo; left_centre 1.30 (off 1.40 x def 0.93): Siosifa Talakai</t>
   </si>
   <si>
     <t xml:space="preserve">16:05</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">penrith panthers</t>
   </si>
   <si>
-    <t xml:space="preserve">right_centre 1.40 (off 1.13 x def 1.24): Hugo Savala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left_centre 1.51 (off 1.34 x def 1.13): Casey McLean; right_wing 1.30 (off 1.32 x def 0.99): Thomas Jenkins</t>
+    <t xml:space="preserve">right_centre 1.46 (off 1.12 x def 1.30): Fetalaiga Pauga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left_centre 1.51 (off 1.41 x def 1.07): Casey McLean; right_wing 1.32 (off 1.35 x def 0.98): Thomas Jenkins</t>
   </si>
   <si>
     <t xml:space="preserve">match_id</t>
@@ -224,118 +224,118 @@
     <t xml:space="preserve">Bradman Best (last 2026-08-30, high_jersey_inferred)</t>
   </si>
   <si>
+    <t xml:space="preserve">positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga (last 2026-08-30, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai (last 2026-08-30, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt (last 2026-08-30, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham (last 2026-09-04, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton (last 2026-09-04, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray (last 2026-09-04, role_not_side_specific)</t>
+  </si>
+  <si>
     <t xml:space="preserve">strong</t>
   </si>
   <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga (last 2026-08-30, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai (last 2026-08-30, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt (last 2026-08-30, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham (last 2026-08-29, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton (last 2026-08-29, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Dufty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Dufty (last 2026-08-29, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallis Duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallis Duncan (last 2026-08-29, high_jersey_inferred)</t>
+    <t xml:space="preserve">Latrell Mitchell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latrell Mitchell (last 2026-09-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Alex Johnston</t>
   </si>
   <si>
-    <t xml:space="preserve">Alex Johnston (last 2026-08-29, high_jersey_inferred)</t>
+    <t xml:space="preserve">Alex Johnston (last 2026-09-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">sched-2026-20260912-1805-warriors-dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo (last 2026-08-29, high_jersey_inferred)</t>
+    <t xml:space="preserve">Tevita Naufahu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Naufahu (last 2026-09-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Herbie Farnworth</t>
   </si>
   <si>
-    <t xml:space="preserve">Herbie Farnworth (last 2026-08-29, high_jersey_inferred)</t>
+    <t xml:space="preserve">Herbie Farnworth (last 2026-09-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
   </si>
   <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow (last 2026-08-29, role_not_side_specific)</t>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow (last 2026-09-04, role_not_side_specific)</t>
   </si>
   <si>
     <t xml:space="preserve">Jack Bostock</t>
   </si>
   <si>
-    <t xml:space="preserve">Jack Bostock (last 2026-08-29, high_jersey_inferred)</t>
+    <t xml:space="preserve">Jack Bostock (last 2026-09-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Jamayne Isaako</t>
   </si>
   <si>
-    <t xml:space="preserve">Jamayne Isaako (last 2026-08-29, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive</t>
+    <t xml:space="preserve">Jamayne Isaako (last 2026-09-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Alofiana Khan-Pereira</t>
   </si>
   <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira (last 2026-08-30, high_jersey_inferred)</t>
+    <t xml:space="preserve">Alofiana Khan-Pereira (last 2026-09-05, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Adam Pompey</t>
   </si>
   <si>
-    <t xml:space="preserve">Adam Pompey (last 2026-08-30, bench_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taine Tuaupiki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taine Tuaupiki (last 2026-08-30, role_not_side_specific)</t>
+    <t xml:space="preserve">Adam Pompey (last 2026-09-05, bench_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad (last 2026-09-05, bench_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Ali Leiataua</t>
   </si>
   <si>
-    <t xml:space="preserve">Ali Leiataua (last 2026-08-30, high_jersey_inferred)</t>
+    <t xml:space="preserve">Ali Leiataua (last 2026-09-05, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Luke Laulilii</t>
@@ -350,61 +350,61 @@
     <t xml:space="preserve">Ronaldo Mulitalo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ronaldo Mulitalo (last 2026-08-30, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KL Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KL Iro (last 2026-08-30, high_jersey_inferred)</t>
+    <t xml:space="preserve">Ronaldo Mulitalo (last 2026-09-05, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai (last 2026-09-05, bench_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">William Kennedy</t>
   </si>
   <si>
-    <t xml:space="preserve">William Kennedy (last 2026-08-30, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mawene Hiroti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mawene Hiroti (last 2026-08-30, high_jersey_inferred)</t>
+    <t xml:space="preserve">William Kennedy (last 2026-09-05, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley Jones (last 2026-09-05, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Sione Katoa</t>
   </si>
   <si>
-    <t xml:space="preserve">Sione Katoa (last 2026-08-30, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Laybutt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Laybutt (last 2026-08-29, high_jersey_inferred)</t>
+    <t xml:space="preserve">Sione Katoa (last 2026-09-05, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Derby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Derby (last 2026-09-05, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Tom Chester</t>
   </si>
   <si>
-    <t xml:space="preserve">Tom Chester (last 2026-08-29, high_jersey_inferred)</t>
+    <t xml:space="preserve">Tom Chester (last 2026-09-05, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Scott Drinkwater</t>
   </si>
   <si>
-    <t xml:space="preserve">Scott Drinkwater (last 2026-08-29, role_not_side_specific)</t>
+    <t xml:space="preserve">Scott Drinkwater (last 2026-09-05, role_not_side_specific)</t>
   </si>
   <si>
     <t xml:space="preserve">Jaxon Purdue</t>
   </si>
   <si>
-    <t xml:space="preserve">Jaxon Purdue (last 2026-08-29, high_jersey_inferred)</t>
+    <t xml:space="preserve">Jaxon Purdue (last 2026-09-05, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Braidon Burns</t>
   </si>
   <si>
-    <t xml:space="preserve">Braidon Burns (last 2026-08-29, high_jersey_inferred)</t>
+    <t xml:space="preserve">Braidon Burns (last 2026-09-05, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">sched-2026-20260913-1605-penrith-panthers-sydney-roosters</t>
@@ -413,61 +413,61 @@
     <t xml:space="preserve">Brian To'o</t>
   </si>
   <si>
-    <t xml:space="preserve">Brian To'o (last 2026-08-28, high_jersey_inferred)</t>
+    <t xml:space="preserve">Brian To'o (last 2026-09-06, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Casey McLean</t>
   </si>
   <si>
-    <t xml:space="preserve">Casey McLean (last 2026-08-28, high_jersey_inferred)</t>
+    <t xml:space="preserve">Casey McLean (last 2026-09-06, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Dylan Edwards</t>
   </si>
   <si>
-    <t xml:space="preserve">Dylan Edwards (last 2026-08-28, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago (last 2026-08-28, high_jersey_inferred)</t>
+    <t xml:space="preserve">Dylan Edwards (last 2026-09-06, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Garner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Garner (last 2026-09-06, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Thomas Jenkins</t>
   </si>
   <si>
-    <t xml:space="preserve">Thomas Jenkins (last 2026-08-28, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase (last 2026-08-29, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia (last 2026-08-29, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco (last 2026-08-29, role_not_side_specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Savala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Savala (last 2026-08-29, high_jersey_inferred)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith (last 2026-08-29, high_jersey_inferred)</t>
+    <t xml:space="preserve">Thomas Jenkins (last 2026-09-06, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rex Bassingthwaighte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rex Bassingthwaighte (last 2026-09-04, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommy Talau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommy Talau (last 2026-09-04, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Ramsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Ramsey (last 2026-09-04, role_not_side_specific)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetalaiga Pauga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetalaiga Pauga (last 2026-09-04, high_jersey_inferred)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Tupou (last 2026-09-04, high_jersey_inferred)</t>
   </si>
   <si>
     <t xml:space="preserve">team_name</t>
@@ -1000,31 +1000,31 @@
         <v>26</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="L2" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="N2" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="M2" s="4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="N2" s="4" t="n">
-        <v>0.98</v>
-      </c>
       <c r="O2" s="4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="P2" s="4" t="n">
         <v>0.45</v>
@@ -1033,16 +1033,16 @@
         <v>0.65</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="V2" s="3" t="s">
         <v>27</v>
@@ -1068,46 +1068,46 @@
         <v>28</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="L3" s="4" t="n">
         <v>0.69</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" s="4" t="n">
         <v>1.42</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>0.65</v>
@@ -1136,49 +1136,49 @@
         <v>26</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="S4" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="T4" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="T4" s="4" t="n">
-        <v>0.92</v>
-      </c>
       <c r="U4" s="4" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>34</v>
@@ -1204,49 +1204,49 @@
         <v>28</v>
       </c>
       <c r="G5" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>1.11</v>
-      </c>
       <c r="M5" s="4" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="O5" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="Q5" s="4" t="n">
         <v>0.92</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0.93</v>
       </c>
       <c r="R5" s="4" t="n">
         <v>1.03</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="V5" s="3" t="s">
         <v>35</v>
@@ -1272,49 +1272,49 @@
         <v>26</v>
       </c>
       <c r="G6" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N6" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="O6" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T6" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="I6" s="4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="U6" s="4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="V6" s="3" t="s">
         <v>39</v>
@@ -1343,46 +1343,46 @@
         <v>1.17</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>0.93</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="S7" s="4" t="n">
         <v>0.87</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="V7" s="3" t="s">
         <v>40</v>
@@ -1408,49 +1408,49 @@
         <v>26</v>
       </c>
       <c r="G8" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M8" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="J8" s="4" t="n">
+      <c r="N8" s="4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O8" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>0.93</v>
-      </c>
       <c r="P8" s="4" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>45</v>
@@ -1476,49 +1476,49 @@
         <v>28</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.96</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>1.51</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.56</v>
+        <v>0.57</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>46</v>
@@ -1567,7 +1567,7 @@
     <col min="18" max="18" width="11.8575" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="19.575" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="12.715" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="18.7175" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="20.4325" hidden="0" customWidth="1"/>
     <col min="22" max="22" width="53.0175" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1662,7 +1662,7 @@
         <v>26</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>4.9881</v>
+        <v>4.9477</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>6</v>
@@ -1677,25 +1677,25 @@
         <v>0.1833</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>1.1486</v>
+        <v>1.1421</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.1334</v>
+        <v>0.1402</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.8362</v>
+        <v>0.8735</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.9605</v>
+        <v>0.9977</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.7736</v>
+        <v>0.8017</v>
       </c>
       <c r="T2" s="3" t="s">
         <v>64</v>
@@ -1730,7 +1730,7 @@
         <v>26</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>4.9881</v>
+        <v>4.9477</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
@@ -1745,25 +1745,25 @@
         <v>0.0851</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.9067</v>
+        <v>0.9003</v>
       </c>
       <c r="N3" s="4" t="n">
         <v>18</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.0911</v>
+        <v>0.0895</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>0.9714</v>
+        <v>0.9467</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0.8808</v>
+        <v>0.8523</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.4171</v>
+        <v>0.4034</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>64</v>
@@ -1798,7 +1798,7 @@
         <v>26</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>4.9881</v>
+        <v>4.9477</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>12</v>
@@ -1810,28 +1810,28 @@
         <v>178</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0957</v>
+        <v>0.0958</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.9803</v>
+        <v>0.9717</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>27</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.1335</v>
+        <v>0.1311</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>1.3674</v>
+        <v>1.3302</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1.3405</v>
+        <v>1.2926</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.6605</v>
+        <v>0.6377</v>
       </c>
       <c r="T4" s="3" t="s">
         <v>69</v>
@@ -1866,7 +1866,7 @@
         <v>26</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>4.9881</v>
+        <v>4.9477</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
@@ -1878,28 +1878,28 @@
         <v>178</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.0591</v>
+        <v>0.059</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.6478</v>
+        <v>0.6536</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.0629</v>
+        <v>0.0617</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.6898</v>
+        <v>0.6833</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.4469</v>
+        <v>0.4465</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.2057</v>
+        <v>0.2018</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>72</v>
@@ -1934,7 +1934,7 @@
         <v>26</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.9881</v>
+        <v>4.9477</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>18</v>
@@ -1946,28 +1946,28 @@
         <v>178</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1826</v>
+        <v>0.1825</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.2019</v>
+        <v>1.2104</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1329</v>
+        <v>0.1349</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.8743</v>
+        <v>0.8946</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.0508</v>
+        <v>1.0828</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.8061</v>
+        <v>0.8175</v>
       </c>
       <c r="T6" s="3" t="s">
         <v>64</v>
@@ -2002,22 +2002,22 @@
         <v>28</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.0016</v>
+        <v>5.4423</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.13</v>
+        <v>0.1332</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.8146</v>
+        <v>0.8297</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>31</v>
@@ -2026,16 +2026,16 @@
         <v>223</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1404</v>
+        <v>0.1405</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.8799</v>
+        <v>0.875</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.7167</v>
+        <v>0.726</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.5668</v>
+        <v>0.624</v>
       </c>
       <c r="T7" s="3" t="s">
         <v>72</v>
@@ -2070,7 +2070,7 @@
         <v>28</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.0016</v>
+        <v>5.4423</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>9</v>
@@ -2079,13 +2079,13 @@
         <v>9</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0495</v>
+        <v>0.0474</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.528</v>
+        <v>0.5009</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>14</v>
@@ -2097,13 +2097,13 @@
         <v>0.0649</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.6914</v>
+        <v>0.6865</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.3651</v>
+        <v>0.3439</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.1698</v>
+        <v>0.1741</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>72</v>
@@ -2138,7 +2138,7 @@
         <v>28</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.0016</v>
+        <v>5.4423</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>12</v>
@@ -2147,13 +2147,13 @@
         <v>15</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.0781</v>
+        <v>0.0747</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.8004</v>
+        <v>0.7577</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>24</v>
@@ -2165,13 +2165,13 @@
         <v>0.107</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.0958</v>
+        <v>1.086</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.8771</v>
+        <v>0.8229</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.4243</v>
+        <v>0.4342</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>64</v>
@@ -2206,22 +2206,22 @@
         <v>28</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.0016</v>
+        <v>5.4423</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1295</v>
+        <v>0.1281</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.4206</v>
+        <v>1.4195</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>28</v>
@@ -2230,25 +2230,25 @@
         <v>223</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1233</v>
+        <v>0.1232</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.3519</v>
+        <v>1.3649</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.9205</v>
+        <v>1.9375</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.8679</v>
+        <v>0.9364</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
@@ -2274,22 +2274,22 @@
         <v>28</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.0016</v>
+        <v>5.4423</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2426</v>
+        <v>0.2361</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.5965</v>
+        <v>1.5655</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>21</v>
@@ -2301,22 +2301,22 @@
         <v>0.098</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.6452</v>
+        <v>0.6496</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.03</v>
+        <v>1.0169</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.7758</v>
+        <v>0.8211</v>
       </c>
       <c r="T11" s="3" t="s">
         <v>64</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
@@ -2327,7 +2327,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>31</v>
@@ -2342,7 +2342,7 @@
         <v>26</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.0201</v>
+        <v>4.3236</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>6</v>
@@ -2351,40 +2351,40 @@
         <v>35</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.152</v>
+        <v>0.1497</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.9529</v>
+        <v>0.9324</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1746</v>
+        <v>0.1809</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.0942</v>
+        <v>1.1271</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.0426</v>
+        <v>1.051</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.654</v>
+        <v>0.7132</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>64</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -2395,7 +2395,7 @@
         <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>31</v>
@@ -2410,49 +2410,49 @@
         <v>26</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.0201</v>
+        <v>4.3236</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1275</v>
+        <v>0.1295</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.3596</v>
+        <v>1.3701</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1286</v>
+        <v>0.1362</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.3707</v>
+        <v>1.4404</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1.8635</v>
+        <v>1.9735</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.6872</v>
+        <v>0.7887</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2463,7 +2463,7 @@
         <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>31</v>
@@ -2478,49 +2478,49 @@
         <v>26</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.0201</v>
+        <v>4.3236</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.148</v>
+        <v>0.1537</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.5166</v>
+        <v>1.5596</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>17</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.1061</v>
+        <v>0.1032</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.0867</v>
+        <v>1.0473</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.6481</v>
+        <v>1.6334</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.6324</v>
+        <v>0.6804</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -2531,7 +2531,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>31</v>
@@ -2546,7 +2546,7 @@
         <v>26</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.0201</v>
+        <v>4.3236</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>15</v>
@@ -2555,40 +2555,40 @@
         <v>17</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.0747</v>
+        <v>0.0735</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8197</v>
+        <v>0.8141</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.0941</v>
+        <v>0.0969</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.0315</v>
+        <v>1.0737</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.8455</v>
+        <v>0.8741</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.303</v>
+        <v>0.3335</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>64</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
@@ -2599,7 +2599,7 @@
         <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>26</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.0201</v>
+        <v>4.3236</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>18</v>
@@ -2623,40 +2623,40 @@
         <v>32</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1394</v>
+        <v>0.1371</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9173</v>
+        <v>0.9091</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>24</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.151</v>
+        <v>0.1467</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.9939</v>
+        <v>0.973</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.9118</v>
+        <v>0.8845</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.5447</v>
+        <v>0.5639</v>
       </c>
       <c r="T16" s="3" t="s">
         <v>64</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -2667,7 +2667,7 @@
         <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>31</v>
@@ -2682,7 +2682,7 @@
         <v>28</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5.166</v>
+        <v>5.1812</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>6</v>
@@ -2691,34 +2691,34 @@
         <v>38</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1771</v>
+        <v>0.1726</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.1099</v>
+        <v>1.0754</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1621</v>
+        <v>0.1646</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.0159</v>
+        <v>1.0255</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.1275</v>
+        <v>1.1028</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.9071</v>
+        <v>0.9168</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>99</v>
@@ -2735,7 +2735,7 @@
         <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>31</v>
@@ -2750,40 +2750,40 @@
         <v>28</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5.166</v>
+        <v>5.1812</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.059</v>
+        <v>0.0618</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.6285</v>
+        <v>0.6532</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1039</v>
+        <v>0.1072</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.1073</v>
+        <v>1.1339</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.6959</v>
+        <v>0.7407</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.3292</v>
+        <v>0.3627</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>72</v>
@@ -2803,7 +2803,7 @@
         <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>31</v>
@@ -2818,40 +2818,40 @@
         <v>28</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.166</v>
+        <v>5.1812</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.0705</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5173</v>
+        <v>0.7158</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.0897</v>
+        <v>0.0885</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.9187</v>
+        <v>0.8977</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.4752</v>
+        <v>0.6426</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.2339</v>
+        <v>0.3279</v>
       </c>
       <c r="T19" s="3" t="s">
         <v>72</v>
@@ -2871,7 +2871,7 @@
         <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>31</v>
@@ -2886,7 +2886,7 @@
         <v>28</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.166</v>
+        <v>5.1812</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>15</v>
@@ -2895,31 +2895,31 @@
         <v>18</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.085</v>
+        <v>0.0827</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.932</v>
+        <v>0.9167</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>18</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.094</v>
+        <v>0.0926</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.031</v>
+        <v>1.0258</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.9609</v>
+        <v>0.9404</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.4417</v>
+        <v>0.4396</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>64</v>
@@ -2939,7 +2939,7 @@
         <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>31</v>
@@ -2954,7 +2954,7 @@
         <v>28</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.166</v>
+        <v>5.1812</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>18</v>
@@ -2963,31 +2963,31 @@
         <v>29</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.1373</v>
+        <v>0.1337</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9032</v>
+        <v>0.8863</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.1422</v>
+        <v>0.1401</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.9357</v>
+        <v>0.9287</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.8451</v>
+        <v>0.8231</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.6475</v>
+        <v>0.6429</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>64</v>
@@ -3022,7 +3022,7 @@
         <v>28</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>5.4686</v>
+        <v>5.9328</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>6</v>
@@ -3031,34 +3031,34 @@
         <v>34</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1462</v>
+        <v>0.1445</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.9164</v>
+        <v>0.9004</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.203</v>
+        <v>0.2084</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.2724</v>
+        <v>1.2985</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.166</v>
+        <v>1.1692</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.0198</v>
+        <v>1.1185</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>110</v>
@@ -3090,7 +3090,7 @@
         <v>28</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>5.4686</v>
+        <v>5.9328</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>9</v>
@@ -3099,31 +3099,31 @@
         <v>32</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.134</v>
+        <v>0.1325</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.4285</v>
+        <v>1.401</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>21</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.0904</v>
+        <v>0.0876</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.9633</v>
+        <v>0.9265</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.3762</v>
+        <v>1.2981</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.7076</v>
+        <v>0.7314</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>69</v>
@@ -3158,7 +3158,7 @@
         <v>28</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.4686</v>
+        <v>5.9328</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>12</v>
@@ -3167,31 +3167,31 @@
         <v>18</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0782</v>
+        <v>0.0774</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.8017</v>
+        <v>0.7852</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.0906</v>
+        <v>0.0917</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.9283</v>
+        <v>0.9309</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.7442</v>
+        <v>0.731</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.3982</v>
+        <v>0.4293</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>72</v>
@@ -3226,40 +3226,40 @@
         <v>28</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5.4686</v>
+        <v>5.9328</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.0578</v>
+        <v>0.061</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.6343</v>
+        <v>0.6763</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>19</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.0822</v>
+        <v>0.0795</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.9012</v>
+        <v>0.8813</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.5716</v>
+        <v>0.5961</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.2857</v>
+        <v>0.3206</v>
       </c>
       <c r="T25" s="3" t="s">
         <v>72</v>
@@ -3294,40 +3294,40 @@
         <v>28</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.4686</v>
+        <v>5.9328</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1457</v>
+        <v>0.1479</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.959</v>
+        <v>0.9805</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>32</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.1383</v>
+        <v>0.1339</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.91</v>
+        <v>0.8879</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.8727</v>
+        <v>0.8706</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.7269</v>
+        <v>0.7825</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>64</v>
@@ -3362,7 +3362,7 @@
         <v>26</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.83</v>
+        <v>3.8478</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>6</v>
@@ -3371,31 +3371,31 @@
         <v>32</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.1622</v>
+        <v>0.1586</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.0167</v>
+        <v>0.9878</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1645</v>
+        <v>0.1662</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1.0312</v>
+        <v>1.0354</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.0484</v>
+        <v>1.0228</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.6459</v>
+        <v>0.6391</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>64</v>
@@ -3430,7 +3430,7 @@
         <v>26</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.83</v>
+        <v>3.8478</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>9</v>
@@ -3439,34 +3439,34 @@
         <v>16</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0822</v>
+        <v>0.0803</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.8759</v>
+        <v>0.8497</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>16</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0818</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.8884</v>
+        <v>0.8656</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.7782</v>
+        <v>0.7355</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.2818</v>
+        <v>0.2707</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="U28" s="3" t="s">
         <v>122</v>
@@ -3498,40 +3498,40 @@
         <v>26</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.83</v>
+        <v>3.8478</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1012</v>
+        <v>0.1036</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.0371</v>
+        <v>1.0509</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.0789</v>
+        <v>0.0821</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.808</v>
+        <v>0.8335</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.838</v>
+        <v>0.8759</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.3158</v>
+        <v>0.336</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>64</v>
@@ -3566,7 +3566,7 @@
         <v>26</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.83</v>
+        <v>3.8478</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>15</v>
@@ -3575,34 +3575,34 @@
         <v>23</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1148</v>
+        <v>0.1121</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.2594</v>
+        <v>1.2423</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>22</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1117</v>
+        <v>0.1096</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.2252</v>
+        <v>1.2137</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.5431</v>
+        <v>1.5078</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.5432</v>
+        <v>0.5297</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U30" s="3" t="s">
         <v>126</v>
@@ -3634,43 +3634,43 @@
         <v>26</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.83</v>
+        <v>3.8478</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1523</v>
+        <v>0.1533</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.002</v>
+        <v>1.0163</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>34</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1735</v>
+        <v>0.1702</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1.1416</v>
+        <v>1.1282</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>1.1439</v>
+        <v>1.1466</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.6711</v>
+        <v>0.6731</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="U31" s="3" t="s">
         <v>128</v>
@@ -3702,40 +3702,40 @@
         <v>28</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.2857</v>
+        <v>4.3032</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1536</v>
+        <v>0.1534</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.9627</v>
+        <v>0.9554</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1308</v>
+        <v>0.1341</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.8198</v>
+        <v>0.8355</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.7892</v>
+        <v>0.7983</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.5339</v>
+        <v>0.5466</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>64</v>
@@ -3770,43 +3770,43 @@
         <v>28</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.2857</v>
+        <v>4.3032</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1255</v>
+        <v>0.1338</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.3379</v>
+        <v>1.4149</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1059</v>
+        <v>0.101</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>1.1291</v>
+        <v>1.0683</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>1.5106</v>
+        <v>1.5115</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.6009</v>
+        <v>0.6096</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>133</v>
@@ -3838,40 +3838,40 @@
         <v>28</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.2857</v>
+        <v>4.3032</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.0859</v>
+        <v>0.0875</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.8801</v>
+        <v>0.888</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>22</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1161</v>
+        <v>0.1107</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1.1892</v>
+        <v>1.1232</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>1.0466</v>
+        <v>0.9974</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.4332</v>
+        <v>0.4193</v>
       </c>
       <c r="T34" s="3" t="s">
         <v>64</v>
@@ -3906,7 +3906,7 @@
         <v>28</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>4.2857</v>
+        <v>4.3032</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>15</v>
@@ -3915,31 +3915,31 @@
         <v>14</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.0616</v>
+        <v>0.0599</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.6755</v>
+        <v>0.6632</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.0762</v>
+        <v>0.0772</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.8352</v>
+        <v>0.8553</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.5642</v>
+        <v>0.5673</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>0.2181</v>
+        <v>0.2184</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>72</v>
@@ -3974,43 +3974,43 @@
         <v>28</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>4.2857</v>
+        <v>4.3032</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.2009</v>
+        <v>0.2032</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>1.3222</v>
+        <v>1.347</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0.1499</v>
+        <v>0.1475</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>0.9865</v>
+        <v>0.9779</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>1.3044</v>
+        <v>1.3172</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>0.8405</v>
+        <v>0.8474</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U36" s="3" t="s">
         <v>139</v>
@@ -4042,40 +4042,40 @@
         <v>26</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>3.5553</v>
+        <v>3.9777</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.1796</v>
+        <v>0.1888</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>1.1259</v>
+        <v>1.1759</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>0.1427</v>
+        <v>0.1469</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>0.8947</v>
+        <v>0.9154</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>1.0073</v>
+        <v>1.0764</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.5909</v>
+        <v>0.7079</v>
       </c>
       <c r="T37" s="3" t="s">
         <v>64</v>
@@ -4110,7 +4110,7 @@
         <v>26</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>3.5553</v>
+        <v>3.9777</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>9</v>
@@ -4119,31 +4119,31 @@
         <v>22</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.0948</v>
+        <v>0.0933</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>1.0102</v>
+        <v>0.9869</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>13</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.0843</v>
+        <v>0.0834</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>0.8988</v>
+        <v>0.8822</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>0.9079</v>
+        <v>0.8706</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.3131</v>
+        <v>0.3372</v>
       </c>
       <c r="T38" s="3" t="s">
         <v>64</v>
@@ -4178,7 +4178,7 @@
         <v>26</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>3.5553</v>
+        <v>3.9777</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>12</v>
@@ -4187,31 +4187,31 @@
         <v>26</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.1094</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>1.1386</v>
+        <v>1.1105</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>14</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>0.0905</v>
+        <v>0.0895</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>0.927</v>
+        <v>0.9084</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>1.0555</v>
+        <v>1.0088</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>0.3788</v>
+        <v>0.4073</v>
       </c>
       <c r="T39" s="3" t="s">
         <v>64</v>
@@ -4246,7 +4246,7 @@
         <v>26</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>3.5553</v>
+        <v>3.9777</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>15</v>
@@ -4255,34 +4255,34 @@
         <v>24</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.101</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>1.1259</v>
+        <v>1.1186</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.1131</v>
+        <v>0.1175</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>1.2408</v>
+        <v>1.3017</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>1.3971</v>
+        <v>1.4562</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.4683</v>
+        <v>0.5385</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="U40" s="3" t="s">
         <v>147</v>
@@ -4314,40 +4314,40 @@
         <v>26</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>3.5553</v>
+        <v>3.9777</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.1751</v>
+        <v>0.1762</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>1.1525</v>
+        <v>1.1686</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>16</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P41" s="4" t="n">
-        <v>0.1072</v>
+        <v>0.1058</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>0.7052</v>
+        <v>0.7017</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>0.8127</v>
+        <v>0.82</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>0.454</v>
+        <v>0.5066</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>64</v>
@@ -4425,25 +4425,25 @@
         <v>30</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1486</v>
+        <v>0.1447</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.9316</v>
+        <v>0.9017</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.1175</v>
+        <v>0.1199</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.7364</v>
+        <v>0.7467</v>
       </c>
     </row>
     <row r="3">
@@ -4457,25 +4457,25 @@
         <v>25</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.121</v>
+        <v>0.1178</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1.29</v>
+        <v>1.2463</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>21</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.0996</v>
+        <v>0.0979</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1.0614</v>
+        <v>1.0353</v>
       </c>
     </row>
     <row r="4">
@@ -4489,25 +4489,25 @@
         <v>23</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1122</v>
+        <v>0.1092</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.1491</v>
+        <v>1.1084</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>27</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.1264</v>
+        <v>0.1242</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1.2948</v>
+        <v>1.2608</v>
       </c>
     </row>
     <row r="5">
@@ -4521,25 +4521,25 @@
         <v>21</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.1026</v>
+        <v>0.0998</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.1248</v>
+        <v>1.1052</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>21</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.0994</v>
+        <v>0.0976</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1.0899</v>
+        <v>1.0811</v>
       </c>
     </row>
     <row r="6">
@@ -4550,28 +4550,28 @@
         <v>18</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1298</v>
+        <v>0.1352</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.8543</v>
+        <v>0.8963</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>37</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1745</v>
+        <v>0.1714</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.1482</v>
+        <v>1.1362</v>
       </c>
     </row>
     <row r="7">
@@ -4582,28 +4582,28 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1165</v>
+        <v>0.1253</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.7299</v>
+        <v>0.7805</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>38</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1869</v>
+        <v>0.1827</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.1712</v>
+        <v>1.1384</v>
       </c>
     </row>
     <row r="8">
@@ -4617,25 +4617,25 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.0768</v>
+        <v>0.0742</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.8183</v>
+        <v>0.7849</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>25</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1221</v>
+        <v>0.1194</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.3019</v>
+        <v>1.2632</v>
       </c>
     </row>
     <row r="9">
@@ -4646,28 +4646,28 @@
         <v>12</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1209</v>
+        <v>0.1211</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.2385</v>
+        <v>1.2288</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.0809</v>
+        <v>0.0837</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.8292</v>
+        <v>0.8492</v>
       </c>
     </row>
     <row r="10">
@@ -4681,25 +4681,25 @@
         <v>24</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1117</v>
+        <v>0.1078</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.2247</v>
+        <v>1.1945</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>16</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.0805</v>
+        <v>0.0786</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.8824</v>
+        <v>0.8706</v>
       </c>
     </row>
     <row r="11">
@@ -4713,25 +4713,25 @@
         <v>24</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1159</v>
+        <v>0.1119</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.7629</v>
+        <v>0.7421</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1356</v>
+        <v>0.137</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.8925</v>
+        <v>0.9084</v>
       </c>
     </row>
     <row r="12">
@@ -4742,28 +4742,28 @@
         <v>6</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1355</v>
+        <v>0.1378</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8491</v>
+        <v>0.8587</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>38</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2101</v>
+        <v>0.2039</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.3169</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="13">
@@ -4777,25 +4777,25 @@
         <v>13</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.074</v>
+        <v>0.0726</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7887</v>
+        <v>0.7675</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>10</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.0596</v>
+        <v>0.0579</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.6353</v>
+        <v>0.6119</v>
       </c>
     </row>
     <row r="14">
@@ -4809,25 +4809,25 @@
         <v>11</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.0641</v>
+        <v>0.0629</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6566</v>
+        <v>0.6381</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>12</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.0703</v>
+        <v>0.0682</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7199</v>
+        <v>0.6923</v>
       </c>
     </row>
     <row r="15">
@@ -4841,25 +4841,25 @@
         <v>16</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.0891</v>
+        <v>0.0872</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.977</v>
+        <v>0.9663</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>11</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.0646</v>
+        <v>0.0625</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.708</v>
+        <v>0.6928</v>
       </c>
     </row>
     <row r="16">
@@ -4873,25 +4873,25 @@
         <v>23</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1298</v>
+        <v>0.1271</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8539</v>
+        <v>0.8425</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2095</v>
+        <v>0.2131</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.3786</v>
+        <v>1.4132</v>
       </c>
     </row>
     <row r="17">
@@ -4905,25 +4905,25 @@
         <v>34</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1462</v>
+        <v>0.1445</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.9164</v>
+        <v>0.9004</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1645</v>
+        <v>0.1662</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.0312</v>
+        <v>1.0354</v>
       </c>
     </row>
     <row r="18">
@@ -4937,25 +4937,25 @@
         <v>32</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.134</v>
+        <v>0.1325</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.4285</v>
+        <v>1.401</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>16</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0818</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8884</v>
+        <v>0.8656</v>
       </c>
     </row>
     <row r="19">
@@ -4969,25 +4969,25 @@
         <v>18</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.0782</v>
+        <v>0.0774</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8017</v>
+        <v>0.7852</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.0789</v>
+        <v>0.0821</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.808</v>
+        <v>0.8335</v>
       </c>
     </row>
     <row r="20">
@@ -4998,28 +4998,28 @@
         <v>15</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.0578</v>
+        <v>0.061</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6343</v>
+        <v>0.6763</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>22</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1117</v>
+        <v>0.1096</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.2252</v>
+        <v>1.2137</v>
       </c>
     </row>
     <row r="21">
@@ -5030,28 +5030,28 @@
         <v>18</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1457</v>
+        <v>0.1479</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.959</v>
+        <v>0.9805</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>34</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1735</v>
+        <v>0.1702</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.1416</v>
+        <v>1.1282</v>
       </c>
     </row>
     <row r="22">
@@ -5065,25 +5065,25 @@
         <v>35</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.152</v>
+        <v>0.1497</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.9529</v>
+        <v>0.9324</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1621</v>
+        <v>0.1646</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.0159</v>
+        <v>1.0255</v>
       </c>
     </row>
     <row r="23">
@@ -5094,28 +5094,28 @@
         <v>9</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1275</v>
+        <v>0.1295</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.3596</v>
+        <v>1.3701</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1039</v>
+        <v>0.1072</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.1073</v>
+        <v>1.1339</v>
       </c>
     </row>
     <row r="24">
@@ -5126,28 +5126,28 @@
         <v>12</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.148</v>
+        <v>0.1537</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.5166</v>
+        <v>1.5596</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>17</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.0897</v>
+        <v>0.0885</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.9187</v>
+        <v>0.8977</v>
       </c>
     </row>
     <row r="25">
@@ -5161,25 +5161,25 @@
         <v>17</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.0747</v>
+        <v>0.0735</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.8197</v>
+        <v>0.8141</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.094</v>
+        <v>0.0926</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.031</v>
+        <v>1.0258</v>
       </c>
     </row>
     <row r="26">
@@ -5193,25 +5193,25 @@
         <v>32</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1394</v>
+        <v>0.1371</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.9173</v>
+        <v>0.9091</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>27</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1422</v>
+        <v>0.1401</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.9357</v>
+        <v>0.9287</v>
       </c>
     </row>
     <row r="27">
@@ -5225,25 +5225,25 @@
         <v>31</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1775</v>
+        <v>0.1748</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.1126</v>
+        <v>1.0891</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>39</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.163</v>
+        <v>0.1605</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.0213</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="28">
@@ -5254,28 +5254,28 @@
         <v>9</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1032</v>
+        <v>0.1068</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.0999</v>
+        <v>1.13</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.0804</v>
+        <v>0.0831</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8571</v>
+        <v>0.8785</v>
       </c>
     </row>
     <row r="29">
@@ -5289,25 +5289,25 @@
         <v>7</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.0453</v>
+        <v>0.0447</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4641</v>
+        <v>0.4533</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.0924</v>
+        <v>0.0988</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.9467</v>
+        <v>1.0021</v>
       </c>
     </row>
     <row r="30">
@@ -5321,25 +5321,25 @@
         <v>16</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.0924</v>
+        <v>0.0909</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.0132</v>
+        <v>1.0066</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>26</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.1077</v>
+        <v>0.106</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.181</v>
+        <v>1.174</v>
       </c>
     </row>
     <row r="31">
@@ -5353,25 +5353,25 @@
         <v>22</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.1293</v>
+        <v>0.1272</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.8507</v>
+        <v>0.8431</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>34</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.1429</v>
+        <v>0.1406</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.9402</v>
+        <v>0.9322</v>
       </c>
     </row>
     <row r="32">
@@ -5382,28 +5382,28 @@
         <v>6</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1713</v>
+        <v>0.1764</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.0739</v>
+        <v>1.0988</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>33</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1743</v>
+        <v>0.1694</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.0923</v>
+        <v>1.0551</v>
       </c>
     </row>
     <row r="33">
@@ -5414,28 +5414,28 @@
         <v>9</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.0956</v>
+        <v>0.1022</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.0187</v>
+        <v>1.0813</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.0809</v>
+        <v>0.0834</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.8623</v>
+        <v>0.8821</v>
       </c>
     </row>
     <row r="34">
@@ -5449,25 +5449,25 @@
         <v>19</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.0914</v>
+        <v>0.0895</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.9363</v>
+        <v>0.9079</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.0861</v>
+        <v>0.1075</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.882</v>
+        <v>1.091</v>
       </c>
     </row>
     <row r="35">
@@ -5478,28 +5478,28 @@
         <v>15</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1487</v>
+        <v>0.1498</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.631</v>
+        <v>1.6592</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.0758</v>
+        <v>0.0735</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.8311</v>
+        <v>0.8148</v>
       </c>
     </row>
     <row r="36">
@@ -5513,25 +5513,25 @@
         <v>27</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.1308</v>
+        <v>0.1279</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.8608</v>
+        <v>0.8479</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>31</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>0.1639</v>
+        <v>0.1591</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.0785</v>
+        <v>1.055</v>
       </c>
     </row>
     <row r="37">
@@ -5542,28 +5542,28 @@
         <v>6</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.1554</v>
+        <v>0.1569</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.9738</v>
+        <v>0.9772</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>38</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>0.1869</v>
+        <v>0.1844</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.1712</v>
+        <v>1.1487</v>
       </c>
     </row>
     <row r="38">
@@ -5577,25 +5577,25 @@
         <v>18</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.0747</v>
+        <v>0.0736</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.7965</v>
+        <v>0.7788</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>21</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0.1037</v>
+        <v>0.1023</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.1054</v>
+        <v>1.0824</v>
       </c>
     </row>
     <row r="39">
@@ -5606,28 +5606,28 @@
         <v>12</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.1477</v>
+        <v>0.1493</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1.5137</v>
+        <v>1.5155</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>16</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0.0809</v>
+        <v>0.0799</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.8292</v>
+        <v>0.8108</v>
       </c>
     </row>
     <row r="40">
@@ -5641,25 +5641,25 @@
         <v>13</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.0554</v>
+        <v>0.0545</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.6076</v>
+        <v>0.6039</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.0851</v>
+        <v>0.0884</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.933</v>
+        <v>0.9792</v>
       </c>
     </row>
     <row r="41">
@@ -5673,25 +5673,25 @@
         <v>36</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.1472</v>
+        <v>0.145</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.969</v>
+        <v>0.9611</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>0.1817</v>
+        <v>0.1837</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.1958</v>
+        <v>1.218</v>
       </c>
     </row>
     <row r="42">
@@ -5711,7 +5711,7 @@
         <v>0.1833</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1.1486</v>
+        <v>1.1421</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>31</v>
@@ -5720,10 +5720,10 @@
         <v>223</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.1404</v>
+        <v>0.1405</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.8799</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="43">
@@ -5743,7 +5743,7 @@
         <v>0.0851</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.9067</v>
+        <v>0.9003</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>14</v>
@@ -5755,7 +5755,7 @@
         <v>0.0649</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0.6914</v>
+        <v>0.6865</v>
       </c>
     </row>
     <row r="44">
@@ -5772,10 +5772,10 @@
         <v>178</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.0957</v>
+        <v>0.0958</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.9803</v>
+        <v>0.9717</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>24</v>
@@ -5787,7 +5787,7 @@
         <v>0.107</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1.0958</v>
+        <v>1.086</v>
       </c>
     </row>
     <row r="45">
@@ -5804,10 +5804,10 @@
         <v>178</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.0591</v>
+        <v>0.059</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.6478</v>
+        <v>0.6536</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>28</v>
@@ -5816,10 +5816,10 @@
         <v>223</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>0.1233</v>
+        <v>0.1232</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.3519</v>
+        <v>1.3649</v>
       </c>
     </row>
     <row r="46">
@@ -5836,10 +5836,10 @@
         <v>178</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.1826</v>
+        <v>0.1825</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1.2019</v>
+        <v>1.2104</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>21</v>
@@ -5851,7 +5851,7 @@
         <v>0.098</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0.6452</v>
+        <v>0.6496</v>
       </c>
     </row>
     <row r="47">
@@ -5865,25 +5865,25 @@
         <v>32</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.1622</v>
+        <v>0.1586</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1.0167</v>
+        <v>0.9878</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>0.203</v>
+        <v>0.2084</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.2724</v>
+        <v>1.2985</v>
       </c>
     </row>
     <row r="48">
@@ -5897,25 +5897,25 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.0822</v>
+        <v>0.0803</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.8759</v>
+        <v>0.8497</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>21</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>0.0904</v>
+        <v>0.0876</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>0.9633</v>
+        <v>0.9265</v>
       </c>
     </row>
     <row r="49">
@@ -5926,28 +5926,28 @@
         <v>12</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.1012</v>
+        <v>0.1036</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.0371</v>
+        <v>1.0509</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>0.0906</v>
+        <v>0.0917</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>0.9283</v>
+        <v>0.9309</v>
       </c>
     </row>
     <row r="50">
@@ -5961,25 +5961,25 @@
         <v>23</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.1148</v>
+        <v>0.1121</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1.2594</v>
+        <v>1.2423</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>19</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.0822</v>
+        <v>0.0795</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>0.9012</v>
+        <v>0.8813</v>
       </c>
     </row>
     <row r="51">
@@ -5990,28 +5990,28 @@
         <v>18</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.1523</v>
+        <v>0.1533</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1.002</v>
+        <v>1.0163</v>
       </c>
       <c r="G51" s="4" t="n">
         <v>32</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.1383</v>
+        <v>0.1339</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>0.91</v>
+        <v>0.8879</v>
       </c>
     </row>
     <row r="52">
@@ -6022,28 +6022,28 @@
         <v>6</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.1503</v>
+        <v>0.1524</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.9419</v>
+        <v>0.9495</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0.1334</v>
+        <v>0.1355</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>0.8362</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="53">
@@ -6054,28 +6054,28 @@
         <v>9</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.0658</v>
+        <v>0.0748</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.7014</v>
+        <v>0.7912</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>24</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0.1114</v>
+        <v>0.1095</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.1871</v>
+        <v>1.1581</v>
       </c>
     </row>
     <row r="54">
@@ -6089,25 +6089,25 @@
         <v>21</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.1187</v>
+        <v>0.1164</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1.2166</v>
+        <v>1.181</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>0.0636</v>
+        <v>0.0626</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>0.6515</v>
+        <v>0.6349</v>
       </c>
     </row>
     <row r="55">
@@ -6121,25 +6121,25 @@
         <v>17</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.0972</v>
+        <v>0.0951</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.0656</v>
+        <v>1.0533</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>0.085</v>
+        <v>0.0835</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>0.932</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="56">
@@ -6153,25 +6153,25 @@
         <v>21</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.1233</v>
+        <v>0.1207</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.8116</v>
+        <v>0.8002</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>40</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>0.1853</v>
+        <v>0.182</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>1.2193</v>
+        <v>1.207</v>
       </c>
     </row>
     <row r="57">
@@ -6182,28 +6182,28 @@
         <v>6</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.1536</v>
+        <v>0.1534</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.9627</v>
+        <v>0.9554</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>0.1427</v>
+        <v>0.1469</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>0.8947</v>
+        <v>0.9154</v>
       </c>
     </row>
     <row r="58">
@@ -6214,28 +6214,28 @@
         <v>9</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.1255</v>
+        <v>0.1338</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1.3379</v>
+        <v>1.4149</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>0.0843</v>
+        <v>0.0834</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>0.8988</v>
+        <v>0.8822</v>
       </c>
     </row>
     <row r="59">
@@ -6246,28 +6246,28 @@
         <v>12</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.0859</v>
+        <v>0.0875</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.8801</v>
+        <v>0.888</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>0.0905</v>
+        <v>0.0895</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>0.927</v>
+        <v>0.9084</v>
       </c>
     </row>
     <row r="60">
@@ -6281,25 +6281,25 @@
         <v>14</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.0616</v>
+        <v>0.0599</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.6755</v>
+        <v>0.6632</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0.1131</v>
+        <v>0.1175</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>1.2408</v>
+        <v>1.3017</v>
       </c>
     </row>
     <row r="61">
@@ -6310,28 +6310,28 @@
         <v>18</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.2009</v>
+        <v>0.2032</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1.3222</v>
+        <v>1.347</v>
       </c>
       <c r="G61" s="4" t="n">
         <v>16</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>0.1072</v>
+        <v>0.1058</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>0.7052</v>
+        <v>0.7017</v>
       </c>
     </row>
     <row r="62">
@@ -6342,28 +6342,28 @@
         <v>6</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.13</v>
+        <v>0.1332</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.8146</v>
+        <v>0.8297</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>0.1334</v>
+        <v>0.1402</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>0.8362</v>
+        <v>0.8735</v>
       </c>
     </row>
     <row r="63">
@@ -6377,25 +6377,25 @@
         <v>9</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.0495</v>
+        <v>0.0474</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.528</v>
+        <v>0.5009</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>0.0911</v>
+        <v>0.0895</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>0.9714</v>
+        <v>0.9467</v>
       </c>
     </row>
     <row r="64">
@@ -6409,25 +6409,25 @@
         <v>15</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.0781</v>
+        <v>0.0747</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.8004</v>
+        <v>0.7577</v>
       </c>
       <c r="G64" s="4" t="n">
         <v>27</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>0.1335</v>
+        <v>0.1311</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>1.3674</v>
+        <v>1.3302</v>
       </c>
     </row>
     <row r="65">
@@ -6438,28 +6438,28 @@
         <v>15</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.1295</v>
+        <v>0.1281</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1.4206</v>
+        <v>1.4195</v>
       </c>
       <c r="G65" s="4" t="n">
         <v>12</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>0.0629</v>
+        <v>0.0617</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>0.6898</v>
+        <v>0.6833</v>
       </c>
     </row>
     <row r="66">
@@ -6470,28 +6470,28 @@
         <v>18</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.2426</v>
+        <v>0.2361</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1.5965</v>
+        <v>1.5655</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>0.1329</v>
+        <v>0.1349</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>0.8743</v>
+        <v>0.8946</v>
       </c>
     </row>
     <row r="67">
@@ -6502,28 +6502,28 @@
         <v>6</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.2081</v>
+        <v>0.2092</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1.3046</v>
+        <v>1.3034</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>0.1737</v>
+        <v>0.175</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>1.0886</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="68">
@@ -6537,25 +6537,25 @@
         <v>20</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.1295</v>
+        <v>0.1265</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1.3808</v>
+        <v>1.3385</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0.0796</v>
+        <v>0.0864</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>0.8485</v>
+        <v>0.9138</v>
       </c>
     </row>
     <row r="69">
@@ -6569,25 +6569,25 @@
         <v>15</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.0998</v>
+        <v>0.0975</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1.0222</v>
+        <v>0.9895</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>27</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>0.1166</v>
+        <v>0.1148</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>1.1944</v>
+        <v>1.1646</v>
       </c>
     </row>
     <row r="70">
@@ -6601,25 +6601,25 @@
         <v>7</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.051</v>
+        <v>0.0497</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0.5589</v>
+        <v>0.5503</v>
       </c>
       <c r="G70" s="4" t="n">
         <v>25</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>0.108</v>
+        <v>0.1062</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>1.1845</v>
+        <v>1.1766</v>
       </c>
     </row>
     <row r="71">
@@ -6633,25 +6633,25 @@
         <v>27</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>0.1773</v>
+        <v>0.173</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1.1668</v>
+        <v>1.1472</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>33</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>0.1446</v>
+        <v>0.1422</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>0.9517</v>
+        <v>0.943</v>
       </c>
     </row>
     <row r="72">
@@ -6662,28 +6662,28 @@
         <v>6</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0.1796</v>
+        <v>0.1888</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1.1259</v>
+        <v>1.1759</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0.1308</v>
+        <v>0.1341</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0.8198</v>
+        <v>0.8355</v>
       </c>
     </row>
     <row r="73">
@@ -6697,25 +6697,25 @@
         <v>22</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0.0948</v>
+        <v>0.0933</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1.0102</v>
+        <v>0.9869</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0.1059</v>
+        <v>0.101</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1.1291</v>
+        <v>1.0683</v>
       </c>
     </row>
     <row r="74">
@@ -6729,25 +6729,25 @@
         <v>26</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.1094</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1.1386</v>
+        <v>1.1105</v>
       </c>
       <c r="G74" s="4" t="n">
         <v>22</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0.1161</v>
+        <v>0.1107</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>1.1892</v>
+        <v>1.1232</v>
       </c>
     </row>
     <row r="75">
@@ -6761,25 +6761,25 @@
         <v>24</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.101</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1.1259</v>
+        <v>1.1186</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>0.0762</v>
+        <v>0.0772</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>0.8352</v>
+        <v>0.8553</v>
       </c>
     </row>
     <row r="76">
@@ -6790,28 +6790,28 @@
         <v>18</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>0.1751</v>
+        <v>0.1762</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1.1525</v>
+        <v>1.1686</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>0.1499</v>
+        <v>0.1475</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>0.9865</v>
+        <v>0.9779</v>
       </c>
     </row>
     <row r="77">
@@ -6825,25 +6825,25 @@
         <v>38</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>0.1771</v>
+        <v>0.1726</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1.1099</v>
+        <v>1.0754</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>0.1746</v>
+        <v>0.1809</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>1.0942</v>
+        <v>1.1271</v>
       </c>
     </row>
     <row r="78">
@@ -6854,28 +6854,28 @@
         <v>9</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>0.059</v>
+        <v>0.0618</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0.6285</v>
+        <v>0.6532</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>0.1286</v>
+        <v>0.1362</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>1.3707</v>
+        <v>1.4404</v>
       </c>
     </row>
     <row r="79">
@@ -6886,28 +6886,28 @@
         <v>12</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.0705</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0.5173</v>
+        <v>0.7158</v>
       </c>
       <c r="G79" s="4" t="n">
         <v>17</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>0.1061</v>
+        <v>0.1032</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>1.0867</v>
+        <v>1.0473</v>
       </c>
     </row>
     <row r="80">
@@ -6921,25 +6921,25 @@
         <v>18</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>0.085</v>
+        <v>0.0827</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0.932</v>
+        <v>0.9167</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0.0941</v>
+        <v>0.0969</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>1.0315</v>
+        <v>1.0737</v>
       </c>
     </row>
     <row r="81">
@@ -6953,25 +6953,25 @@
         <v>29</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>0.1373</v>
+        <v>0.1337</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0.9032</v>
+        <v>0.8863</v>
       </c>
       <c r="G81" s="4" t="n">
         <v>24</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>0.151</v>
+        <v>0.1467</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>0.9939</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="82">
@@ -6982,25 +6982,25 @@
         <v>6</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>0.185</v>
+        <v>0.1886</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1.1592</v>
+        <v>1.1748</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>0.1195</v>
+        <v>0.1202</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>0.7488</v>
@@ -7017,25 +7017,25 @@
         <v>14</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>0.0881</v>
+        <v>0.0872</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0.9389</v>
+        <v>0.9218</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>0.1109</v>
+        <v>0.12</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>1.1821</v>
+        <v>1.2689</v>
       </c>
     </row>
     <row r="84">
@@ -7049,25 +7049,25 @@
         <v>14</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>0.0884</v>
+        <v>0.0875</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0.9059</v>
+        <v>0.888</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>0.1237</v>
+        <v>0.1243</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>1.2673</v>
+        <v>1.2613</v>
       </c>
     </row>
     <row r="85">
@@ -7078,28 +7078,28 @@
         <v>15</v>
       </c>
       <c r="C85" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>0.1276</v>
+        <v>0.1317</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1.3996</v>
+        <v>1.4592</v>
       </c>
       <c r="G85" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>0.0814</v>
+        <v>0.079</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>0.893</v>
+        <v>0.8757</v>
       </c>
     </row>
     <row r="86">
@@ -7113,25 +7113,25 @@
         <v>18</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>0.1161</v>
+        <v>0.1147</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>0.7639</v>
+        <v>0.7604</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>0.1566</v>
+        <v>0.1602</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>1.0307</v>
+        <v>1.0623</v>
       </c>
     </row>
   </sheetData>
